--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Maces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E01F7CC-16D6-401A-9E4B-6C84F521D419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F54A258-AD46-43C0-87A3-AB00AACECF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13276,7 +13276,7 @@
         <v>46176.469560185185</v>
       </c>
       <c r="J471">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K471" t="s">
         <v>11</v>
@@ -13334,7 +13334,7 @@
         <v>46176.469560185185</v>
       </c>
       <c r="J473">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K473" t="s">
         <v>11</v>
@@ -13363,7 +13363,7 @@
         <v>46176.470254629632</v>
       </c>
       <c r="J474">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K474" t="s">
         <v>11</v>
@@ -13392,7 +13392,7 @@
         <v>46176.470254629632</v>
       </c>
       <c r="J475">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K475" t="s">
         <v>11</v>
@@ -13421,7 +13421,7 @@
         <v>46176.470254629632</v>
       </c>
       <c r="J476">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K476" t="s">
         <v>11</v>
@@ -13450,7 +13450,7 @@
         <v>46176.470949074072</v>
       </c>
       <c r="J477">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K477" t="s">
         <v>11</v>
@@ -13479,7 +13479,7 @@
         <v>46176.470949074072</v>
       </c>
       <c r="J478">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K478" t="s">
         <v>11</v>
@@ -13508,7 +13508,7 @@
         <v>46176.471643518518</v>
       </c>
       <c r="J479">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K479" t="s">
         <v>11</v>
@@ -13537,7 +13537,7 @@
         <v>46176.471643518518</v>
       </c>
       <c r="J480">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K480" t="s">
         <v>11</v>
@@ -13566,7 +13566,7 @@
         <v>46176.472337962965</v>
       </c>
       <c r="J481">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K481" t="s">
         <v>11</v>
@@ -13595,7 +13595,7 @@
         <v>46176.472337962965</v>
       </c>
       <c r="J482">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K482" t="s">
         <v>11</v>
@@ -13624,7 +13624,7 @@
         <v>46176.472337962965</v>
       </c>
       <c r="J483">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K483" t="s">
         <v>11</v>
@@ -13653,7 +13653,7 @@
         <v>46176.473032407404</v>
       </c>
       <c r="J484">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K484" t="s">
         <v>11</v>
@@ -13711,7 +13711,7 @@
         <v>46176.473726851851</v>
       </c>
       <c r="J486">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K486" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Maces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39232DFB-55B8-4688-8BA6-CAA60DC67446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE6A54DB-2130-43BE-A3B0-C8D2ECC809CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -86,6 +86,9 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>Vehicle Inspections</t>
+  </si>
+  <si>
     <t>Winter Weather</t>
   </si>
   <si>
@@ -95,10 +98,19 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
+    <t>Distracted Driving</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
+  </si>
+  <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
@@ -110,13 +122,7 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Safe Lifting for Commercial Drivers</t>
-  </si>
-  <si>
     <t>DNU-Driver Health</t>
-  </si>
-  <si>
-    <t>DNU-Fatigue</t>
   </si>
   <si>
     <t>DNU-Scene of an Accident</t>
@@ -125,34 +131,28 @@
     <t>DNU-NEW-Vehicle Inspections</t>
   </si>
   <si>
-    <t>Vehicle Inspections</t>
+    <t>Work Zone Safety</t>
   </si>
   <si>
-    <t>Distracted Driving</t>
+    <t>Micro-Learn Speed</t>
+  </si>
+  <si>
+    <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Dangers of Aggressive Driving for CMV Drivers</t>
+  </si>
+  <si>
+    <t>3 points of contact</t>
   </si>
   <si>
     <t>Safe RR Crossing</t>
   </si>
   <si>
-    <t>3 points of contact</t>
-  </si>
-  <si>
     <t>In Cab Distractions</t>
   </si>
   <si>
-    <t>Micro-Learn Speed</t>
-  </si>
-  <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Fire Extinguisher Training for CDL</t>
+    <t>DNU-Fatigue</t>
   </si>
   <si>
     <t>Bryan Brown</t>
@@ -646,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -704,7 +704,7 @@
         <v>40</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -733,7 +733,7 @@
         <v>38</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -762,7 +762,7 @@
         <v>41</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -791,7 +791,7 @@
         <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -820,7 +820,7 @@
         <v>43</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -849,7 +849,7 @@
         <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -878,7 +878,7 @@
         <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -907,7 +907,7 @@
         <v>46</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -936,7 +936,7 @@
         <v>47</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -965,7 +965,7 @@
         <v>48</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -994,7 +994,7 @@
         <v>49</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -1023,7 +1023,7 @@
         <v>50</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -1052,7 +1052,7 @@
         <v>51</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -1081,7 +1081,7 @@
         <v>52</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         <v>53</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1139,7 +1139,7 @@
         <v>54</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>40</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>13</v>
@@ -1197,7 +1197,7 @@
         <v>38</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1226,7 +1226,7 @@
         <v>41</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1255,7 +1255,7 @@
         <v>42</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>44</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>13</v>
@@ -1313,7 +1313,7 @@
         <v>54</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1342,7 +1342,7 @@
         <v>45</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>13</v>
@@ -1371,7 +1371,7 @@
         <v>46</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>14</v>
@@ -1395,7 +1395,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="M26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
@@ -1409,7 +1409,7 @@
         <v>47</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>13</v>
@@ -1438,7 +1438,7 @@
         <v>55</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>12</v>
@@ -1462,7 +1462,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="1"/>
       <c r="M29" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
@@ -1476,7 +1476,7 @@
         <v>48</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1505,7 +1505,7 @@
         <v>49</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1534,7 +1534,7 @@
         <v>50</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>12</v>
@@ -1558,7 +1558,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="1"/>
       <c r="M33" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
@@ -1572,7 +1572,7 @@
         <v>51</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1601,7 +1601,7 @@
         <v>52</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1630,7 +1630,7 @@
         <v>53</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>14</v>
@@ -1654,7 +1654,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="1"/>
       <c r="M37" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
@@ -1668,7 +1668,7 @@
         <v>40</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>13</v>
@@ -1697,7 +1697,7 @@
         <v>38</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1726,7 +1726,7 @@
         <v>56</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>13</v>
@@ -1755,7 +1755,7 @@
         <v>41</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1784,7 +1784,7 @@
         <v>44</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>13</v>
@@ -1813,7 +1813,7 @@
         <v>54</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>45</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
@@ -1871,7 +1871,7 @@
         <v>46</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1900,7 +1900,7 @@
         <v>47</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>13</v>
@@ -1929,7 +1929,7 @@
         <v>55</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -1958,7 +1958,7 @@
         <v>48</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1987,7 +1987,7 @@
         <v>49</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
@@ -2016,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -2045,7 +2045,7 @@
         <v>52</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -2074,7 +2074,7 @@
         <v>53</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>13</v>
@@ -2103,7 +2103,7 @@
         <v>40</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>13</v>
@@ -2132,7 +2132,7 @@
         <v>38</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2161,7 +2161,7 @@
         <v>57</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2190,7 +2190,7 @@
         <v>56</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -2219,7 +2219,7 @@
         <v>41</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2248,7 +2248,7 @@
         <v>58</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2277,7 +2277,7 @@
         <v>44</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2306,7 +2306,7 @@
         <v>54</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2335,7 +2335,7 @@
         <v>45</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2364,7 +2364,7 @@
         <v>46</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2393,7 +2393,7 @@
         <v>47</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>14</v>
@@ -2417,7 +2417,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="1"/>
       <c r="M64" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
@@ -2431,7 +2431,7 @@
         <v>55</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>14</v>
@@ -2455,7 +2455,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="1"/>
       <c r="M66" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
@@ -2469,7 +2469,7 @@
         <v>48</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2498,7 +2498,7 @@
         <v>49</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2527,7 +2527,7 @@
         <v>51</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>13</v>
@@ -2556,7 +2556,7 @@
         <v>52</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>13</v>
@@ -2585,7 +2585,7 @@
         <v>59</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2614,7 +2614,7 @@
         <v>53</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2643,7 +2643,7 @@
         <v>40</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2672,7 +2672,7 @@
         <v>56</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>13</v>
@@ -2701,7 +2701,7 @@
         <v>44</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2730,7 +2730,7 @@
         <v>54</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2759,7 +2759,7 @@
         <v>45</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>13</v>
@@ -2788,7 +2788,7 @@
         <v>46</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>13</v>
@@ -2817,7 +2817,7 @@
         <v>47</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2846,7 +2846,7 @@
         <v>55</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>13</v>
@@ -2875,7 +2875,7 @@
         <v>51</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2904,7 +2904,7 @@
         <v>52</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>13</v>
@@ -2933,7 +2933,7 @@
         <v>53</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>13</v>
@@ -2962,7 +2962,7 @@
         <v>40</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>13</v>
@@ -2991,7 +2991,7 @@
         <v>57</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>56</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -3049,7 +3049,7 @@
         <v>41</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -3078,7 +3078,7 @@
         <v>58</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>10</v>
@@ -3107,7 +3107,7 @@
         <v>44</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -3136,7 +3136,7 @@
         <v>54</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3165,7 +3165,7 @@
         <v>45</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>14</v>
@@ -3189,7 +3189,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="1"/>
       <c r="M92" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
@@ -3203,7 +3203,7 @@
         <v>46</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -3232,7 +3232,7 @@
         <v>47</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3261,7 +3261,7 @@
         <v>55</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3290,7 +3290,7 @@
         <v>48</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>10</v>
@@ -3319,7 +3319,7 @@
         <v>49</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>10</v>
@@ -3348,7 +3348,7 @@
         <v>51</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3377,7 +3377,7 @@
         <v>52</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>13</v>
@@ -3406,7 +3406,7 @@
         <v>59</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3435,7 +3435,7 @@
         <v>53</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>13</v>
@@ -3464,7 +3464,7 @@
         <v>40</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>13</v>
@@ -3493,7 +3493,7 @@
         <v>60</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>12</v>
@@ -3517,7 +3517,7 @@
       <c r="J104" s="2"/>
       <c r="K104" s="1"/>
       <c r="M104" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
@@ -3531,7 +3531,7 @@
         <v>57</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3560,7 +3560,7 @@
         <v>41</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3589,7 +3589,7 @@
         <v>58</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>12</v>
@@ -3613,7 +3613,7 @@
       <c r="J108" s="2"/>
       <c r="K108" s="1"/>
       <c r="M108" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
@@ -3627,7 +3627,7 @@
         <v>44</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>13</v>
@@ -3656,7 +3656,7 @@
         <v>54</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>13</v>
@@ -3685,7 +3685,7 @@
         <v>45</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>14</v>
@@ -3709,7 +3709,7 @@
       <c r="J112" s="2"/>
       <c r="K112" s="1"/>
       <c r="M112" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
@@ -3723,7 +3723,7 @@
         <v>46</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>12</v>
@@ -3747,7 +3747,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
       <c r="M114" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
@@ -3761,7 +3761,7 @@
         <v>47</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3790,7 +3790,7 @@
         <v>55</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>13</v>
@@ -3819,7 +3819,7 @@
         <v>48</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>10</v>
@@ -3848,7 +3848,7 @@
         <v>49</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -3877,7 +3877,7 @@
         <v>51</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -3906,7 +3906,7 @@
         <v>52</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3935,7 +3935,7 @@
         <v>59</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -3964,7 +3964,7 @@
         <v>53</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>13</v>
@@ -3993,7 +3993,7 @@
         <v>40</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -4022,7 +4022,7 @@
         <v>60</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>12</v>
@@ -4046,7 +4046,7 @@
       <c r="J125" s="2"/>
       <c r="K125" s="1"/>
       <c r="M125" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
@@ -4060,7 +4060,7 @@
         <v>57</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -4089,7 +4089,7 @@
         <v>41</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>10</v>
@@ -4118,7 +4118,7 @@
         <v>58</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>12</v>
@@ -4142,7 +4142,7 @@
       <c r="J129" s="2"/>
       <c r="K129" s="1"/>
       <c r="M129" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
@@ -4156,7 +4156,7 @@
         <v>44</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4185,7 +4185,7 @@
         <v>45</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>13</v>
@@ -4214,7 +4214,7 @@
         <v>46</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>10</v>
@@ -4243,7 +4243,7 @@
         <v>47</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4272,7 +4272,7 @@
         <v>55</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4301,7 +4301,7 @@
         <v>48</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4330,7 +4330,7 @@
         <v>49</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>10</v>
@@ -4359,7 +4359,7 @@
         <v>51</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>13</v>
@@ -4388,7 +4388,7 @@
         <v>52</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>13</v>
@@ -4417,7 +4417,7 @@
         <v>59</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>10</v>
@@ -4446,7 +4446,7 @@
         <v>53</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>10</v>
@@ -4475,7 +4475,7 @@
         <v>40</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>12</v>
@@ -4499,7 +4499,7 @@
       <c r="J142" s="2"/>
       <c r="K142" s="1"/>
       <c r="M142" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
@@ -4513,7 +4513,7 @@
         <v>60</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>10</v>
@@ -4542,7 +4542,7 @@
         <v>57</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>10</v>
@@ -4571,7 +4571,7 @@
         <v>41</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>10</v>
@@ -4600,7 +4600,7 @@
         <v>61</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>10</v>
@@ -4629,7 +4629,7 @@
         <v>58</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>13</v>
@@ -4658,7 +4658,7 @@
         <v>44</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4687,7 +4687,7 @@
         <v>45</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>12</v>
@@ -4711,7 +4711,7 @@
       <c r="J150" s="2"/>
       <c r="K150" s="1"/>
       <c r="M150" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
@@ -4725,7 +4725,7 @@
         <v>46</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>10</v>
@@ -4754,7 +4754,7 @@
         <v>47</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>10</v>
@@ -4783,7 +4783,7 @@
         <v>55</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>10</v>
@@ -4812,7 +4812,7 @@
         <v>48</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>10</v>
@@ -4841,7 +4841,7 @@
         <v>49</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>10</v>
@@ -4870,7 +4870,7 @@
         <v>62</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>10</v>
@@ -4899,7 +4899,7 @@
         <v>51</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>10</v>
@@ -4928,7 +4928,7 @@
         <v>52</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -4957,7 +4957,7 @@
         <v>63</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>12</v>
@@ -4981,7 +4981,7 @@
       <c r="J160" s="2"/>
       <c r="K160" s="1"/>
       <c r="M160" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
@@ -4995,7 +4995,7 @@
         <v>59</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>10</v>
@@ -5024,7 +5024,7 @@
         <v>53</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>12</v>
@@ -5048,7 +5048,7 @@
       <c r="J163" s="2"/>
       <c r="K163" s="1"/>
       <c r="M163" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
@@ -5062,7 +5062,7 @@
         <v>40</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>13</v>
@@ -5091,7 +5091,7 @@
         <v>60</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>10</v>
@@ -5120,7 +5120,7 @@
         <v>57</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>13</v>
@@ -5149,7 +5149,7 @@
         <v>41</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>10</v>
@@ -5178,7 +5178,7 @@
         <v>61</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>10</v>
@@ -5207,7 +5207,7 @@
         <v>58</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>13</v>
@@ -5236,7 +5236,7 @@
         <v>44</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>13</v>
@@ -5265,7 +5265,7 @@
         <v>45</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>10</v>
@@ -5294,7 +5294,7 @@
         <v>46</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>10</v>
@@ -5323,7 +5323,7 @@
         <v>47</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>13</v>
@@ -5352,7 +5352,7 @@
         <v>55</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>13</v>
@@ -5381,7 +5381,7 @@
         <v>48</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>10</v>
@@ -5410,7 +5410,7 @@
         <v>49</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>10</v>
@@ -5439,7 +5439,7 @@
         <v>62</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>10</v>
@@ -5468,7 +5468,7 @@
         <v>51</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>12</v>
@@ -5492,7 +5492,7 @@
       <c r="J179" s="2"/>
       <c r="K179" s="1"/>
       <c r="M179" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="180" spans="4:13" x14ac:dyDescent="0.3">
@@ -5506,7 +5506,7 @@
         <v>52</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>13</v>
@@ -5535,7 +5535,7 @@
         <v>63</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>13</v>
@@ -5564,7 +5564,7 @@
         <v>59</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>10</v>
@@ -5593,7 +5593,7 @@
         <v>53</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>10</v>
@@ -5622,7 +5622,7 @@
         <v>40</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>13</v>
@@ -5651,7 +5651,7 @@
         <v>60</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>10</v>
@@ -5680,7 +5680,7 @@
         <v>57</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>13</v>
@@ -5709,7 +5709,7 @@
         <v>41</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>10</v>
@@ -5738,7 +5738,7 @@
         <v>61</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>10</v>
@@ -5767,7 +5767,7 @@
         <v>58</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>13</v>
@@ -5796,7 +5796,7 @@
         <v>45</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>14</v>
@@ -5820,7 +5820,7 @@
       <c r="J191" s="2"/>
       <c r="K191" s="1"/>
       <c r="M191" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="192" spans="4:13" x14ac:dyDescent="0.3">
@@ -5834,7 +5834,7 @@
         <v>46</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>10</v>
@@ -5863,7 +5863,7 @@
         <v>47</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>13</v>
@@ -5892,7 +5892,7 @@
         <v>55</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>13</v>
@@ -5921,7 +5921,7 @@
         <v>64</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>13</v>
@@ -5950,7 +5950,7 @@
         <v>48</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>10</v>
@@ -5979,7 +5979,7 @@
         <v>49</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>12</v>
@@ -6003,7 +6003,7 @@
       <c r="J198" s="2"/>
       <c r="K198" s="1"/>
       <c r="M198" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="199" spans="4:13" x14ac:dyDescent="0.3">
@@ -6017,7 +6017,7 @@
         <v>62</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>10</v>
@@ -6046,7 +6046,7 @@
         <v>51</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>13</v>
@@ -6075,7 +6075,7 @@
         <v>52</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>13</v>
@@ -6104,7 +6104,7 @@
         <v>59</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>10</v>
@@ -6133,7 +6133,7 @@
         <v>53</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>12</v>
@@ -6157,7 +6157,7 @@
       <c r="J204" s="2"/>
       <c r="K204" s="1"/>
       <c r="M204" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="205" spans="4:13" x14ac:dyDescent="0.3">
@@ -6171,7 +6171,7 @@
         <v>40</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>12</v>
@@ -6195,7 +6195,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
       <c r="M206" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="207" spans="4:13" x14ac:dyDescent="0.3">
@@ -6209,7 +6209,7 @@
         <v>65</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>13</v>
@@ -6238,7 +6238,7 @@
         <v>60</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>10</v>
@@ -6267,7 +6267,7 @@
         <v>57</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>12</v>
@@ -6291,7 +6291,7 @@
       <c r="J210" s="2"/>
       <c r="K210" s="1"/>
       <c r="M210" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="211" spans="4:13" x14ac:dyDescent="0.3">
@@ -6305,7 +6305,7 @@
         <v>41</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6334,7 +6334,7 @@
         <v>61</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -6363,7 +6363,7 @@
         <v>58</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>13</v>
@@ -6392,7 +6392,7 @@
         <v>45</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>13</v>
@@ -6421,7 +6421,7 @@
         <v>46</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -6450,7 +6450,7 @@
         <v>47</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>13</v>
@@ -6479,7 +6479,7 @@
         <v>55</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>13</v>
@@ -6508,7 +6508,7 @@
         <v>48</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>10</v>
@@ -6537,7 +6537,7 @@
         <v>49</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>10</v>
@@ -6566,7 +6566,7 @@
         <v>62</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>10</v>
@@ -6595,7 +6595,7 @@
         <v>51</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>13</v>
@@ -6624,7 +6624,7 @@
         <v>52</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>13</v>
@@ -6653,7 +6653,7 @@
         <v>59</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>10</v>
@@ -6682,7 +6682,7 @@
         <v>53</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>13</v>
@@ -6711,7 +6711,7 @@
         <v>40</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>13</v>
@@ -6740,7 +6740,7 @@
         <v>65</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>13</v>
@@ -6769,7 +6769,7 @@
         <v>60</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>13</v>
@@ -6798,7 +6798,7 @@
         <v>57</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>10</v>
@@ -6827,7 +6827,7 @@
         <v>41</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>61</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -6885,7 +6885,7 @@
         <v>58</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>13</v>
@@ -6914,7 +6914,7 @@
         <v>45</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>10</v>
@@ -6943,7 +6943,7 @@
         <v>46</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>10</v>
@@ -6972,7 +6972,7 @@
         <v>47</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>10</v>
@@ -7001,7 +7001,7 @@
         <v>55</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>13</v>
@@ -7030,7 +7030,7 @@
         <v>48</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>10</v>
@@ -7059,7 +7059,7 @@
         <v>49</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>10</v>
@@ -7088,7 +7088,7 @@
         <v>66</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>10</v>
@@ -7117,7 +7117,7 @@
         <v>62</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -7146,7 +7146,7 @@
         <v>51</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>12</v>
@@ -7170,7 +7170,7 @@
       <c r="J241" s="2"/>
       <c r="K241" s="1"/>
       <c r="M241" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="242" spans="4:13" x14ac:dyDescent="0.3">
@@ -7184,7 +7184,7 @@
         <v>52</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>13</v>
@@ -7213,7 +7213,7 @@
         <v>59</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>10</v>
@@ -7242,7 +7242,7 @@
         <v>53</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>13</v>
@@ -7271,7 +7271,7 @@
         <v>40</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>13</v>
@@ -7300,7 +7300,7 @@
         <v>60</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>13</v>
@@ -7329,7 +7329,7 @@
         <v>41</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>10</v>
@@ -7358,7 +7358,7 @@
         <v>61</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>10</v>
@@ -7387,7 +7387,7 @@
         <v>45</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>12</v>
@@ -7411,7 +7411,7 @@
       <c r="J250" s="2"/>
       <c r="K250" s="1"/>
       <c r="M250" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="251" spans="4:13" x14ac:dyDescent="0.3">
@@ -7425,7 +7425,7 @@
         <v>46</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>10</v>
@@ -7454,7 +7454,7 @@
         <v>47</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7483,7 +7483,7 @@
         <v>64</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>10</v>
@@ -7512,7 +7512,7 @@
         <v>48</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>10</v>
@@ -7541,7 +7541,7 @@
         <v>49</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -7570,7 +7570,7 @@
         <v>66</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>13</v>
@@ -7599,7 +7599,7 @@
         <v>51</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -7628,7 +7628,7 @@
         <v>52</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>13</v>
@@ -7657,7 +7657,7 @@
         <v>59</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -7686,7 +7686,7 @@
         <v>40</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>13</v>
@@ -7715,7 +7715,7 @@
         <v>60</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>13</v>
@@ -7744,7 +7744,7 @@
         <v>41</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>14</v>
@@ -7768,7 +7768,7 @@
       <c r="J263" s="2"/>
       <c r="K263" s="1"/>
       <c r="M263" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="264" spans="4:13" x14ac:dyDescent="0.3">
@@ -7782,7 +7782,7 @@
         <v>61</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>10</v>
@@ -7811,7 +7811,7 @@
         <v>67</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>13</v>
@@ -7840,7 +7840,7 @@
         <v>45</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>10</v>
@@ -7869,7 +7869,7 @@
         <v>46</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>10</v>
@@ -7898,7 +7898,7 @@
         <v>47</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>13</v>
@@ -7927,7 +7927,7 @@
         <v>68</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>12</v>
@@ -7951,7 +7951,7 @@
       <c r="J270" s="2"/>
       <c r="K270" s="1"/>
       <c r="M270" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="271" spans="4:13" x14ac:dyDescent="0.3">
@@ -7965,7 +7965,7 @@
         <v>64</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>12</v>
@@ -7989,7 +7989,7 @@
       <c r="J272" s="2"/>
       <c r="K272" s="1"/>
       <c r="M272" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="273" spans="4:13" x14ac:dyDescent="0.3">
@@ -8003,7 +8003,7 @@
         <v>48</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>10</v>
@@ -8032,7 +8032,7 @@
         <v>49</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>10</v>
@@ -8061,7 +8061,7 @@
         <v>66</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>13</v>
@@ -8090,7 +8090,7 @@
         <v>51</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>13</v>
@@ -8119,7 +8119,7 @@
         <v>52</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>13</v>
@@ -8148,7 +8148,7 @@
         <v>69</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>13</v>
@@ -8177,7 +8177,7 @@
         <v>59</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>13</v>
@@ -8206,7 +8206,7 @@
         <v>40</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>13</v>
@@ -8235,7 +8235,7 @@
         <v>70</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>10</v>
@@ -8264,7 +8264,7 @@
         <v>60</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>13</v>
@@ -8293,7 +8293,7 @@
         <v>41</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>12</v>
@@ -8317,7 +8317,7 @@
       <c r="J284" s="2"/>
       <c r="K284" s="1"/>
       <c r="M284" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="285" spans="4:13" x14ac:dyDescent="0.3">
@@ -8331,7 +8331,7 @@
         <v>67</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>13</v>
@@ -8360,7 +8360,7 @@
         <v>45</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>10</v>
@@ -8389,7 +8389,7 @@
         <v>46</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>13</v>
@@ -8418,7 +8418,7 @@
         <v>47</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>13</v>
@@ -8447,7 +8447,7 @@
         <v>68</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>12</v>
@@ -8471,7 +8471,7 @@
       <c r="J290" s="2"/>
       <c r="K290" s="1"/>
       <c r="M290" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="291" spans="4:13" x14ac:dyDescent="0.3">
@@ -8485,7 +8485,7 @@
         <v>64</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>12</v>
@@ -8509,7 +8509,7 @@
       <c r="J292" s="2"/>
       <c r="K292" s="1"/>
       <c r="M292" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="293" spans="4:13" x14ac:dyDescent="0.3">
@@ -8523,7 +8523,7 @@
         <v>48</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>49</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>10</v>
@@ -8581,7 +8581,7 @@
         <v>66</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>13</v>
@@ -8610,7 +8610,7 @@
         <v>51</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>10</v>
@@ -8639,7 +8639,7 @@
         <v>52</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>13</v>
@@ -8668,7 +8668,7 @@
         <v>69</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>13</v>
@@ -8697,7 +8697,7 @@
         <v>59</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>12</v>
@@ -8721,7 +8721,7 @@
       <c r="J300" s="2"/>
       <c r="K300" s="1"/>
       <c r="M300" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="301" spans="4:13" x14ac:dyDescent="0.3">
@@ -8735,7 +8735,7 @@
         <v>40</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>13</v>
@@ -8764,7 +8764,7 @@
         <v>70</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>10</v>
@@ -8793,7 +8793,7 @@
         <v>60</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>13</v>
@@ -8822,7 +8822,7 @@
         <v>41</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>14</v>
@@ -8846,7 +8846,7 @@
       <c r="J305" s="2"/>
       <c r="K305" s="1"/>
       <c r="M305" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="306" spans="4:13" x14ac:dyDescent="0.3">
@@ -8860,7 +8860,7 @@
         <v>45</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -8889,7 +8889,7 @@
         <v>47</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>13</v>
@@ -8918,7 +8918,7 @@
         <v>68</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>12</v>
@@ -8942,7 +8942,7 @@
       <c r="J309" s="2"/>
       <c r="K309" s="1"/>
       <c r="M309" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="310" spans="4:13" x14ac:dyDescent="0.3">
@@ -8956,7 +8956,7 @@
         <v>64</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>10</v>
@@ -8985,7 +8985,7 @@
         <v>48</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>10</v>
@@ -9014,7 +9014,7 @@
         <v>49</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>10</v>
@@ -9043,7 +9043,7 @@
         <v>66</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>13</v>
@@ -9072,7 +9072,7 @@
         <v>51</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>13</v>
@@ -9101,7 +9101,7 @@
         <v>52</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>13</v>
@@ -9130,7 +9130,7 @@
         <v>69</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>13</v>
@@ -9159,7 +9159,7 @@
         <v>59</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>10</v>
@@ -9188,7 +9188,7 @@
         <v>40</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>13</v>
@@ -9217,7 +9217,7 @@
         <v>60</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>13</v>
@@ -9246,7 +9246,7 @@
         <v>41</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>14</v>
@@ -9270,7 +9270,7 @@
       <c r="J321" s="2"/>
       <c r="K321" s="1"/>
       <c r="M321" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="322" spans="4:13" x14ac:dyDescent="0.3">
@@ -9284,7 +9284,7 @@
         <v>45</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>13</v>
@@ -9313,7 +9313,7 @@
         <v>71</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>13</v>
@@ -9342,7 +9342,7 @@
         <v>47</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>13</v>
@@ -9371,7 +9371,7 @@
         <v>68</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>13</v>
@@ -9400,7 +9400,7 @@
         <v>64</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>14</v>
@@ -9424,7 +9424,7 @@
       <c r="J327" s="2"/>
       <c r="K327" s="1"/>
       <c r="M327" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="328" spans="4:13" x14ac:dyDescent="0.3">
@@ -9438,7 +9438,7 @@
         <v>48</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>13</v>
@@ -9467,7 +9467,7 @@
         <v>49</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>10</v>
@@ -9496,7 +9496,7 @@
         <v>66</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>13</v>
@@ -9525,7 +9525,7 @@
         <v>51</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>10</v>
@@ -9554,7 +9554,7 @@
         <v>52</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>13</v>
@@ -9583,7 +9583,7 @@
         <v>69</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>13</v>
@@ -9612,7 +9612,7 @@
         <v>59</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>10</v>
@@ -9641,7 +9641,7 @@
         <v>40</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>14</v>
@@ -9665,7 +9665,7 @@
       <c r="J336" s="2"/>
       <c r="K336" s="1"/>
       <c r="M336" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="337" spans="4:13" x14ac:dyDescent="0.3">
@@ -9679,7 +9679,7 @@
         <v>60</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>13</v>
@@ -9708,7 +9708,7 @@
         <v>41</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>13</v>
@@ -9737,7 +9737,7 @@
         <v>45</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>10</v>
@@ -9766,7 +9766,7 @@
         <v>71</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>10</v>
@@ -9795,7 +9795,7 @@
         <v>47</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>13</v>
@@ -9824,7 +9824,7 @@
         <v>68</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>13</v>
@@ -9853,7 +9853,7 @@
         <v>72</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -9882,7 +9882,7 @@
         <v>64</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>14</v>
@@ -9906,7 +9906,7 @@
       <c r="J345" s="2"/>
       <c r="K345" s="1"/>
       <c r="M345" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="346" spans="4:13" x14ac:dyDescent="0.3">
@@ -9920,7 +9920,7 @@
         <v>48</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>13</v>
@@ -9949,7 +9949,7 @@
         <v>49</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>10</v>
@@ -9978,7 +9978,7 @@
         <v>66</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>13</v>
@@ -10007,7 +10007,7 @@
         <v>51</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>13</v>
@@ -10036,7 +10036,7 @@
         <v>52</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>13</v>
@@ -10065,7 +10065,7 @@
         <v>69</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>13</v>
@@ -10094,7 +10094,7 @@
         <v>59</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>10</v>
@@ -10123,7 +10123,7 @@
         <v>40</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>12</v>
@@ -10147,7 +10147,7 @@
       <c r="J354" s="2"/>
       <c r="K354" s="1"/>
       <c r="M354" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="355" spans="4:13" x14ac:dyDescent="0.3">
@@ -10161,7 +10161,7 @@
         <v>70</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>10</v>
@@ -10190,7 +10190,7 @@
         <v>60</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>13</v>
@@ -10219,7 +10219,7 @@
         <v>41</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>13</v>
@@ -10248,7 +10248,7 @@
         <v>45</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>10</v>
@@ -10277,7 +10277,7 @@
         <v>71</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>13</v>
@@ -10306,7 +10306,7 @@
         <v>68</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>12</v>
@@ -10330,7 +10330,7 @@
       <c r="J361" s="2"/>
       <c r="K361" s="1"/>
       <c r="M361" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="362" spans="4:13" x14ac:dyDescent="0.3">
@@ -10344,7 +10344,7 @@
         <v>72</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>10</v>
@@ -10373,7 +10373,7 @@
         <v>64</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I363" s="1" t="s">
         <v>14</v>
@@ -10397,7 +10397,7 @@
       <c r="J364" s="2"/>
       <c r="K364" s="1"/>
       <c r="M364" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="365" spans="4:13" x14ac:dyDescent="0.3">
@@ -10411,7 +10411,7 @@
         <v>49</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I365" s="1" t="s">
         <v>10</v>
@@ -10440,7 +10440,7 @@
         <v>66</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>13</v>
@@ -10469,7 +10469,7 @@
         <v>51</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>10</v>
@@ -10498,7 +10498,7 @@
         <v>52</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>13</v>
@@ -10527,7 +10527,7 @@
         <v>69</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>13</v>
@@ -10556,7 +10556,7 @@
         <v>59</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>12</v>
@@ -10580,7 +10580,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
       <c r="M371" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="372" spans="4:13" x14ac:dyDescent="0.3">
@@ -10594,7 +10594,7 @@
         <v>40</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>12</v>
@@ -10618,7 +10618,7 @@
       <c r="J373" s="2"/>
       <c r="K373" s="1"/>
       <c r="M373" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="374" spans="4:13" x14ac:dyDescent="0.3">
@@ -10632,7 +10632,7 @@
         <v>70</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>10</v>
@@ -10661,7 +10661,7 @@
         <v>60</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>13</v>
@@ -10690,7 +10690,7 @@
         <v>41</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>10</v>
@@ -10719,7 +10719,7 @@
         <v>45</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>13</v>
@@ -10748,7 +10748,7 @@
         <v>71</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>13</v>
@@ -10777,7 +10777,7 @@
         <v>68</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>13</v>
@@ -10806,7 +10806,7 @@
         <v>72</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>10</v>
@@ -10835,7 +10835,7 @@
         <v>64</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>13</v>
@@ -10864,7 +10864,7 @@
         <v>49</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I382" s="1" t="s">
         <v>10</v>
@@ -10893,7 +10893,7 @@
         <v>66</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>10</v>
@@ -10922,7 +10922,7 @@
         <v>51</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>10</v>
@@ -10951,7 +10951,7 @@
         <v>52</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>13</v>
@@ -10980,7 +10980,7 @@
         <v>69</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>13</v>
@@ -11009,7 +11009,7 @@
         <v>59</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>12</v>
@@ -11033,7 +11033,7 @@
       <c r="J388" s="2"/>
       <c r="K388" s="1"/>
       <c r="M388" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="389" spans="4:13" x14ac:dyDescent="0.3">
@@ -11047,7 +11047,7 @@
         <v>40</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I389" s="1" t="s">
         <v>12</v>
@@ -11071,7 +11071,7 @@
       <c r="J390" s="2"/>
       <c r="K390" s="1"/>
       <c r="M390" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="391" spans="4:13" x14ac:dyDescent="0.3">
@@ -11085,7 +11085,7 @@
         <v>70</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I391" s="1" t="s">
         <v>10</v>
@@ -11114,7 +11114,7 @@
         <v>60</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I392" s="1" t="s">
         <v>12</v>
@@ -11138,7 +11138,7 @@
       <c r="J393" s="2"/>
       <c r="K393" s="1"/>
       <c r="M393" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="394" spans="4:13" x14ac:dyDescent="0.3">
@@ -11152,7 +11152,7 @@
         <v>41</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>13</v>
@@ -11181,7 +11181,7 @@
         <v>45</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>12</v>
@@ -11205,7 +11205,7 @@
       <c r="J396" s="2"/>
       <c r="K396" s="1"/>
       <c r="M396" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="397" spans="4:13" x14ac:dyDescent="0.3">
@@ -11219,7 +11219,7 @@
         <v>71</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I397" s="1" t="s">
         <v>13</v>
@@ -11248,7 +11248,7 @@
         <v>72</v>
       </c>
       <c r="H398" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I398" s="1" t="s">
         <v>10</v>
@@ -11277,7 +11277,7 @@
         <v>64</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>14</v>
@@ -11301,7 +11301,7 @@
       <c r="J400" s="2"/>
       <c r="K400" s="1"/>
       <c r="M400" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="401" spans="4:13" x14ac:dyDescent="0.3">
@@ -11315,7 +11315,7 @@
         <v>49</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I401" s="1" t="s">
         <v>10</v>
@@ -11344,7 +11344,7 @@
         <v>66</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>10</v>
@@ -11373,7 +11373,7 @@
         <v>51</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I403" s="1" t="s">
         <v>10</v>
@@ -11402,7 +11402,7 @@
         <v>52</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I404" s="1" t="s">
         <v>13</v>
@@ -11431,7 +11431,7 @@
         <v>69</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>13</v>
@@ -11460,7 +11460,7 @@
         <v>59</v>
       </c>
       <c r="H406" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I406" s="1" t="s">
         <v>12</v>
@@ -11484,7 +11484,7 @@
       <c r="J407" s="2"/>
       <c r="K407" s="1"/>
       <c r="M407" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="408" spans="4:13" x14ac:dyDescent="0.3">
@@ -11498,7 +11498,7 @@
         <v>40</v>
       </c>
       <c r="H408" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I408" s="1" t="s">
         <v>13</v>
@@ -11527,7 +11527,7 @@
         <v>70</v>
       </c>
       <c r="H409" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I409" s="1" t="s">
         <v>10</v>
@@ -11556,7 +11556,7 @@
         <v>60</v>
       </c>
       <c r="H410" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I410" s="1" t="s">
         <v>13</v>
@@ -11585,7 +11585,7 @@
         <v>41</v>
       </c>
       <c r="H411" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I411" s="1" t="s">
         <v>13</v>
@@ -11614,7 +11614,7 @@
         <v>73</v>
       </c>
       <c r="H412" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I412" s="1" t="s">
         <v>10</v>
@@ -11643,7 +11643,7 @@
         <v>45</v>
       </c>
       <c r="H413" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I413" s="1" t="s">
         <v>13</v>
@@ -11672,7 +11672,7 @@
         <v>71</v>
       </c>
       <c r="H414" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I414" s="1" t="s">
         <v>13</v>
@@ -11701,7 +11701,7 @@
         <v>72</v>
       </c>
       <c r="H415" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I415" s="1" t="s">
         <v>10</v>
@@ -11730,7 +11730,7 @@
         <v>64</v>
       </c>
       <c r="H416" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I416" s="1" t="s">
         <v>13</v>
@@ -11759,7 +11759,7 @@
         <v>49</v>
       </c>
       <c r="H417" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I417" s="1" t="s">
         <v>10</v>
@@ -11788,7 +11788,7 @@
         <v>66</v>
       </c>
       <c r="H418" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I418" s="1" t="s">
         <v>13</v>
@@ -11817,7 +11817,7 @@
         <v>51</v>
       </c>
       <c r="H419" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I419" s="1" t="s">
         <v>10</v>
@@ -11846,7 +11846,7 @@
         <v>52</v>
       </c>
       <c r="H420" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I420" s="1" t="s">
         <v>13</v>
@@ -11875,7 +11875,7 @@
         <v>69</v>
       </c>
       <c r="H421" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I421" s="1" t="s">
         <v>13</v>
@@ -11904,7 +11904,7 @@
         <v>59</v>
       </c>
       <c r="H422" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I422" s="1" t="s">
         <v>13</v>
@@ -11933,7 +11933,7 @@
         <v>74</v>
       </c>
       <c r="H423" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I423" s="1" t="s">
         <v>10</v>
@@ -11962,7 +11962,7 @@
         <v>40</v>
       </c>
       <c r="H424" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I424" s="1" t="s">
         <v>13</v>
@@ -11991,7 +11991,7 @@
         <v>70</v>
       </c>
       <c r="H425" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I425" s="1" t="s">
         <v>10</v>
@@ -12020,7 +12020,7 @@
         <v>60</v>
       </c>
       <c r="H426" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I426" s="1" t="s">
         <v>13</v>
@@ -12049,7 +12049,7 @@
         <v>41</v>
       </c>
       <c r="H427" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I427" s="1" t="s">
         <v>13</v>
@@ -12078,7 +12078,7 @@
         <v>45</v>
       </c>
       <c r="H428" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I428" s="1" t="s">
         <v>13</v>
@@ -12107,7 +12107,7 @@
         <v>72</v>
       </c>
       <c r="H429" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I429" s="1" t="s">
         <v>13</v>
@@ -12136,7 +12136,7 @@
         <v>64</v>
       </c>
       <c r="H430" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I430" s="1" t="s">
         <v>13</v>
@@ -12165,7 +12165,7 @@
         <v>49</v>
       </c>
       <c r="H431" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I431" s="1" t="s">
         <v>13</v>
@@ -12194,7 +12194,7 @@
         <v>66</v>
       </c>
       <c r="H432" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I432" s="1" t="s">
         <v>13</v>
@@ -12223,7 +12223,7 @@
         <v>51</v>
       </c>
       <c r="H433" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I433" s="1" t="s">
         <v>10</v>
@@ -12252,7 +12252,7 @@
         <v>52</v>
       </c>
       <c r="H434" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I434" s="1" t="s">
         <v>13</v>
@@ -12281,7 +12281,7 @@
         <v>69</v>
       </c>
       <c r="H435" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I435" s="1" t="s">
         <v>13</v>
@@ -12310,7 +12310,7 @@
         <v>59</v>
       </c>
       <c r="H436" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I436" s="1" t="s">
         <v>10</v>
@@ -12339,7 +12339,7 @@
         <v>74</v>
       </c>
       <c r="H437" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I437" s="1" t="s">
         <v>13</v>
@@ -12368,7 +12368,7 @@
         <v>40</v>
       </c>
       <c r="H438" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I438" s="1" t="s">
         <v>13</v>
@@ -12397,7 +12397,7 @@
         <v>70</v>
       </c>
       <c r="H439" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I439" s="1" t="s">
         <v>10</v>
@@ -12426,7 +12426,7 @@
         <v>60</v>
       </c>
       <c r="H440" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I440" s="1" t="s">
         <v>13</v>
@@ -12455,7 +12455,7 @@
         <v>41</v>
       </c>
       <c r="H441" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I441" s="1" t="s">
         <v>13</v>
@@ -12484,7 +12484,7 @@
         <v>45</v>
       </c>
       <c r="H442" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I442" s="1" t="s">
         <v>10</v>
@@ -12513,7 +12513,7 @@
         <v>72</v>
       </c>
       <c r="H443" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I443" s="1" t="s">
         <v>13</v>
@@ -12542,7 +12542,7 @@
         <v>64</v>
       </c>
       <c r="H444" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I444" s="1" t="s">
         <v>13</v>
@@ -12571,7 +12571,7 @@
         <v>49</v>
       </c>
       <c r="H445" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I445" s="1" t="s">
         <v>12</v>
@@ -12595,7 +12595,7 @@
       <c r="J446" s="2"/>
       <c r="K446" s="1"/>
       <c r="M446" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="447" spans="4:13" x14ac:dyDescent="0.3">
@@ -12609,7 +12609,7 @@
         <v>66</v>
       </c>
       <c r="H447" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I447" s="1" t="s">
         <v>13</v>
@@ -12638,7 +12638,7 @@
         <v>75</v>
       </c>
       <c r="H448" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I448" s="1" t="s">
         <v>14</v>
@@ -12662,7 +12662,7 @@
       <c r="J449" s="2"/>
       <c r="K449" s="1"/>
       <c r="M449" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="450" spans="4:13" x14ac:dyDescent="0.3">
@@ -12676,7 +12676,7 @@
         <v>51</v>
       </c>
       <c r="H450" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I450" s="1" t="s">
         <v>12</v>
@@ -12700,7 +12700,7 @@
       <c r="J451" s="2"/>
       <c r="K451" s="1"/>
       <c r="M451" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="452" spans="4:13" x14ac:dyDescent="0.3">
@@ -12714,7 +12714,7 @@
         <v>52</v>
       </c>
       <c r="H452" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I452" s="1" t="s">
         <v>13</v>
@@ -12743,7 +12743,7 @@
         <v>59</v>
       </c>
       <c r="H453" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I453" s="1" t="s">
         <v>13</v>
@@ -12772,7 +12772,7 @@
         <v>74</v>
       </c>
       <c r="H454" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>13</v>
@@ -12801,7 +12801,7 @@
         <v>40</v>
       </c>
       <c r="H455" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I455" s="1" t="s">
         <v>13</v>
@@ -12830,7 +12830,7 @@
         <v>70</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I456" s="1" t="s">
         <v>10</v>
@@ -12859,7 +12859,7 @@
         <v>60</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I457" s="1" t="s">
         <v>13</v>
@@ -12888,7 +12888,7 @@
         <v>41</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>13</v>
@@ -12917,7 +12917,7 @@
         <v>67</v>
       </c>
       <c r="H459" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I459" s="1" t="s">
         <v>13</v>
@@ -12946,7 +12946,7 @@
         <v>45</v>
       </c>
       <c r="H460" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I460" s="1" t="s">
         <v>13</v>
@@ -12975,7 +12975,7 @@
         <v>72</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I461" s="1" t="s">
         <v>13</v>
@@ -13004,7 +13004,7 @@
         <v>64</v>
       </c>
       <c r="H462" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I462" s="1" t="s">
         <v>13</v>
@@ -13033,7 +13033,7 @@
         <v>49</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I463" s="1" t="s">
         <v>10</v>
@@ -13062,7 +13062,7 @@
         <v>66</v>
       </c>
       <c r="H464" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I464" s="1" t="s">
         <v>13</v>
@@ -13091,7 +13091,7 @@
         <v>75</v>
       </c>
       <c r="H465" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I465" s="1" t="s">
         <v>10</v>
@@ -13120,7 +13120,7 @@
         <v>51</v>
       </c>
       <c r="H466" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I466" s="1" t="s">
         <v>10</v>
@@ -13149,7 +13149,7 @@
         <v>52</v>
       </c>
       <c r="H467" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I467" s="1" t="s">
         <v>13</v>
@@ -13178,7 +13178,7 @@
         <v>59</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I468" s="1" t="s">
         <v>10</v>
@@ -13207,7 +13207,7 @@
         <v>74</v>
       </c>
       <c r="H469" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I469" s="1" t="s">
         <v>13</v>
@@ -13236,7 +13236,7 @@
         <v>76</v>
       </c>
       <c r="H470" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I470" s="1" t="s">
         <v>10</v>
@@ -13265,7 +13265,7 @@
         <v>40</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I471" s="1" t="s">
         <v>13</v>
@@ -13294,7 +13294,7 @@
         <v>70</v>
       </c>
       <c r="H472" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I472" s="1" t="s">
         <v>10</v>
@@ -13323,7 +13323,7 @@
         <v>60</v>
       </c>
       <c r="H473" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I473" s="1" t="s">
         <v>13</v>
@@ -13352,7 +13352,7 @@
         <v>41</v>
       </c>
       <c r="H474" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I474" s="1" t="s">
         <v>13</v>
@@ -13381,7 +13381,7 @@
         <v>67</v>
       </c>
       <c r="H475" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I475" s="1" t="s">
         <v>13</v>
@@ -13410,7 +13410,7 @@
         <v>45</v>
       </c>
       <c r="H476" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I476" s="1" t="s">
         <v>13</v>
@@ -13439,7 +13439,7 @@
         <v>72</v>
       </c>
       <c r="H477" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I477" s="1" t="s">
         <v>13</v>
@@ -13468,7 +13468,7 @@
         <v>64</v>
       </c>
       <c r="H478" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I478" s="1" t="s">
         <v>13</v>
@@ -13497,7 +13497,7 @@
         <v>49</v>
       </c>
       <c r="H479" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I479" s="1" t="s">
         <v>13</v>
@@ -13526,7 +13526,7 @@
         <v>66</v>
       </c>
       <c r="H480" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I480" s="1" t="s">
         <v>13</v>
@@ -13555,7 +13555,7 @@
         <v>75</v>
       </c>
       <c r="H481" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I481" s="1" t="s">
         <v>13</v>
@@ -13584,7 +13584,7 @@
         <v>77</v>
       </c>
       <c r="H482" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I482" s="1" t="s">
         <v>13</v>
@@ -13613,7 +13613,7 @@
         <v>51</v>
       </c>
       <c r="H483" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I483" s="1" t="s">
         <v>13</v>
@@ -13642,7 +13642,7 @@
         <v>52</v>
       </c>
       <c r="H484" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I484" s="1" t="s">
         <v>13</v>
@@ -13671,7 +13671,7 @@
         <v>59</v>
       </c>
       <c r="H485" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I485" s="1" t="s">
         <v>10</v>
@@ -13700,7 +13700,7 @@
         <v>74</v>
       </c>
       <c r="H486" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I486" s="1" t="s">
         <v>13</v>
@@ -13729,7 +13729,7 @@
         <v>76</v>
       </c>
       <c r="H487" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I487" s="1" t="s">
         <v>10</v>
@@ -15580,6 +15580,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -15654,6 +15655,7 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
@@ -49162,7 +49164,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Maces\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE6A54DB-2130-43BE-A3B0-C8D2ECC809CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{499BD3C3-806D-441F-B441-02BCDA553F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2317" uniqueCount="78">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,7 +86,22 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>DNU-Driver Health</t>
+  </si>
+  <si>
+    <t>DNU-Scene of an Accident</t>
+  </si>
+  <si>
+    <t>DNU-NEW-Vehicle Inspections</t>
+  </si>
+  <si>
     <t>Vehicle Inspections</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -101,13 +116,10 @@
     <t>Distracted Driving</t>
   </si>
   <si>
-    <t>Driver Health</t>
+    <t>Micro-Learn Speed</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Fire Extinguisher Training for CDL</t>
@@ -116,28 +128,16 @@
     <t>Alert Driving: Big Three</t>
   </si>
   <si>
+    <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
+  </si>
+  <si>
     <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Speed Mangement-C</t>
-  </si>
-  <si>
-    <t>DNU-Driver Health</t>
-  </si>
-  <si>
-    <t>DNU-Scene of an Accident</t>
-  </si>
-  <si>
-    <t>DNU-NEW-Vehicle Inspections</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Micro-Learn Speed</t>
-  </si>
-  <si>
-    <t>Safe Lifting for Commercial Drivers</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
@@ -646,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -704,7 +704,7 @@
         <v>40</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -733,7 +733,7 @@
         <v>38</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -762,7 +762,7 @@
         <v>41</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -791,7 +791,7 @@
         <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -820,7 +820,7 @@
         <v>43</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -849,7 +849,7 @@
         <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -878,7 +878,7 @@
         <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -907,7 +907,7 @@
         <v>46</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -936,7 +936,7 @@
         <v>47</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -965,7 +965,7 @@
         <v>48</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -994,7 +994,7 @@
         <v>49</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -1023,7 +1023,7 @@
         <v>50</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -1052,7 +1052,7 @@
         <v>51</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -1081,7 +1081,7 @@
         <v>52</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         <v>53</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1139,7 +1139,7 @@
         <v>54</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1395,7 +1395,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="M26" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
@@ -1462,7 +1462,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="1"/>
       <c r="M29" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
@@ -1558,7 +1558,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="1"/>
       <c r="M33" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
@@ -1654,7 +1654,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="1"/>
       <c r="M37" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
@@ -1668,7 +1668,7 @@
         <v>40</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>13</v>
@@ -1697,7 +1697,7 @@
         <v>38</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1726,7 +1726,7 @@
         <v>56</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>13</v>
@@ -1755,7 +1755,7 @@
         <v>41</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1784,7 +1784,7 @@
         <v>44</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>13</v>
@@ -1813,7 +1813,7 @@
         <v>54</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>45</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
@@ -1871,7 +1871,7 @@
         <v>46</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1900,7 +1900,7 @@
         <v>47</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>13</v>
@@ -1929,7 +1929,7 @@
         <v>55</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>10</v>
@@ -1958,7 +1958,7 @@
         <v>48</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1987,7 +1987,7 @@
         <v>49</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
@@ -2016,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -2045,7 +2045,7 @@
         <v>52</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -2074,7 +2074,7 @@
         <v>53</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>13</v>
@@ -2103,7 +2103,7 @@
         <v>40</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>13</v>
@@ -2132,7 +2132,7 @@
         <v>38</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -2161,7 +2161,7 @@
         <v>57</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2190,7 +2190,7 @@
         <v>56</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>13</v>
@@ -2219,7 +2219,7 @@
         <v>41</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2248,7 +2248,7 @@
         <v>58</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2277,7 +2277,7 @@
         <v>44</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>13</v>
@@ -2306,7 +2306,7 @@
         <v>54</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2335,7 +2335,7 @@
         <v>45</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2364,7 +2364,7 @@
         <v>46</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2393,7 +2393,7 @@
         <v>47</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>14</v>
@@ -2417,7 +2417,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="1"/>
       <c r="M64" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
@@ -2431,7 +2431,7 @@
         <v>55</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>14</v>
@@ -2455,7 +2455,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="1"/>
       <c r="M66" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
@@ -2469,7 +2469,7 @@
         <v>48</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2498,7 +2498,7 @@
         <v>49</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2527,7 +2527,7 @@
         <v>51</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>13</v>
@@ -2556,7 +2556,7 @@
         <v>52</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>13</v>
@@ -2585,7 +2585,7 @@
         <v>59</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2614,7 +2614,7 @@
         <v>53</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>13</v>
@@ -2643,7 +2643,7 @@
         <v>40</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2672,7 +2672,7 @@
         <v>56</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>13</v>
@@ -2701,7 +2701,7 @@
         <v>44</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2730,7 +2730,7 @@
         <v>54</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2759,7 +2759,7 @@
         <v>45</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>13</v>
@@ -2788,7 +2788,7 @@
         <v>46</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>13</v>
@@ -2817,7 +2817,7 @@
         <v>47</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2846,7 +2846,7 @@
         <v>55</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>13</v>
@@ -2875,7 +2875,7 @@
         <v>51</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2904,7 +2904,7 @@
         <v>52</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>13</v>
@@ -2933,7 +2933,7 @@
         <v>53</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>13</v>
@@ -2962,7 +2962,7 @@
         <v>40</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>13</v>
@@ -2991,7 +2991,7 @@
         <v>57</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>56</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -3049,7 +3049,7 @@
         <v>41</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -3078,7 +3078,7 @@
         <v>58</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>10</v>
@@ -3107,7 +3107,7 @@
         <v>44</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -3136,7 +3136,7 @@
         <v>54</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3165,7 +3165,7 @@
         <v>45</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>14</v>
@@ -3189,7 +3189,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="1"/>
       <c r="M92" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
@@ -3203,7 +3203,7 @@
         <v>46</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -3232,7 +3232,7 @@
         <v>47</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3261,7 +3261,7 @@
         <v>55</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3290,7 +3290,7 @@
         <v>48</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>10</v>
@@ -3319,7 +3319,7 @@
         <v>49</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>10</v>
@@ -3348,7 +3348,7 @@
         <v>51</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3377,7 +3377,7 @@
         <v>52</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>13</v>
@@ -3406,7 +3406,7 @@
         <v>59</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3435,7 +3435,7 @@
         <v>53</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>13</v>
@@ -3464,7 +3464,7 @@
         <v>40</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>13</v>
@@ -3493,7 +3493,7 @@
         <v>60</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>12</v>
@@ -3517,7 +3517,7 @@
       <c r="J104" s="2"/>
       <c r="K104" s="1"/>
       <c r="M104" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
@@ -3531,7 +3531,7 @@
         <v>57</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3560,7 +3560,7 @@
         <v>41</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3589,7 +3589,7 @@
         <v>58</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>12</v>
@@ -3613,7 +3613,7 @@
       <c r="J108" s="2"/>
       <c r="K108" s="1"/>
       <c r="M108" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
@@ -3627,7 +3627,7 @@
         <v>44</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>13</v>
@@ -3656,7 +3656,7 @@
         <v>54</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>13</v>
@@ -3685,7 +3685,7 @@
         <v>45</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>14</v>
@@ -3709,7 +3709,7 @@
       <c r="J112" s="2"/>
       <c r="K112" s="1"/>
       <c r="M112" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
@@ -3723,7 +3723,7 @@
         <v>46</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>12</v>
@@ -3747,7 +3747,7 @@
       <c r="J114" s="2"/>
       <c r="K114" s="1"/>
       <c r="M114" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
@@ -3761,7 +3761,7 @@
         <v>47</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3790,7 +3790,7 @@
         <v>55</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>13</v>
@@ -3819,7 +3819,7 @@
         <v>48</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>10</v>
@@ -3848,7 +3848,7 @@
         <v>49</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -3877,7 +3877,7 @@
         <v>51</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -3906,7 +3906,7 @@
         <v>52</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3935,7 +3935,7 @@
         <v>59</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -3964,7 +3964,7 @@
         <v>53</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>13</v>
@@ -3993,7 +3993,7 @@
         <v>40</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -4022,7 +4022,7 @@
         <v>60</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>12</v>
@@ -4046,7 +4046,7 @@
       <c r="J125" s="2"/>
       <c r="K125" s="1"/>
       <c r="M125" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
@@ -4060,7 +4060,7 @@
         <v>57</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -4089,7 +4089,7 @@
         <v>41</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>10</v>
@@ -4118,7 +4118,7 @@
         <v>58</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>12</v>
@@ -4142,7 +4142,7 @@
       <c r="J129" s="2"/>
       <c r="K129" s="1"/>
       <c r="M129" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
@@ -4156,7 +4156,7 @@
         <v>44</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4185,7 +4185,7 @@
         <v>45</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>13</v>
@@ -4214,7 +4214,7 @@
         <v>46</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>10</v>
@@ -4243,7 +4243,7 @@
         <v>47</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4272,7 +4272,7 @@
         <v>55</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4301,7 +4301,7 @@
         <v>48</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4330,7 +4330,7 @@
         <v>49</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>10</v>
@@ -4359,7 +4359,7 @@
         <v>51</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>13</v>
@@ -4388,7 +4388,7 @@
         <v>52</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>13</v>
@@ -4417,7 +4417,7 @@
         <v>59</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>10</v>
@@ -4446,7 +4446,7 @@
         <v>53</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>10</v>
@@ -4475,7 +4475,7 @@
         <v>40</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>12</v>
@@ -4499,7 +4499,7 @@
       <c r="J142" s="2"/>
       <c r="K142" s="1"/>
       <c r="M142" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
@@ -4513,7 +4513,7 @@
         <v>60</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>10</v>
@@ -4542,7 +4542,7 @@
         <v>57</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>10</v>
@@ -4571,7 +4571,7 @@
         <v>41</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>10</v>
@@ -4600,7 +4600,7 @@
         <v>61</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>10</v>
@@ -4629,7 +4629,7 @@
         <v>58</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>13</v>
@@ -4658,7 +4658,7 @@
         <v>44</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4687,7 +4687,7 @@
         <v>45</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>12</v>
@@ -4711,7 +4711,7 @@
       <c r="J150" s="2"/>
       <c r="K150" s="1"/>
       <c r="M150" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
@@ -4725,7 +4725,7 @@
         <v>46</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>10</v>
@@ -4754,7 +4754,7 @@
         <v>47</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>10</v>
@@ -4783,7 +4783,7 @@
         <v>55</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>10</v>
@@ -4812,7 +4812,7 @@
         <v>48</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>10</v>
@@ -4841,7 +4841,7 @@
         <v>49</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>10</v>
@@ -4870,7 +4870,7 @@
         <v>62</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>10</v>
@@ -4899,7 +4899,7 @@
         <v>51</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>10</v>
@@ -4928,7 +4928,7 @@
         <v>52</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -4957,7 +4957,7 @@
         <v>63</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>12</v>
@@ -4981,7 +4981,7 @@
       <c r="J160" s="2"/>
       <c r="K160" s="1"/>
       <c r="M160" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
@@ -4995,7 +4995,7 @@
         <v>59</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>10</v>
@@ -5024,7 +5024,7 @@
         <v>53</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>12</v>
@@ -5048,7 +5048,7 @@
       <c r="J163" s="2"/>
       <c r="K163" s="1"/>
       <c r="M163" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
@@ -5492,7 +5492,7 @@
       <c r="J179" s="2"/>
       <c r="K179" s="1"/>
       <c r="M179" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" spans="4:13" x14ac:dyDescent="0.3">
@@ -5820,7 +5820,7 @@
       <c r="J191" s="2"/>
       <c r="K191" s="1"/>
       <c r="M191" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="192" spans="4:13" x14ac:dyDescent="0.3">
@@ -6003,7 +6003,7 @@
       <c r="J198" s="2"/>
       <c r="K198" s="1"/>
       <c r="M198" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="199" spans="4:13" x14ac:dyDescent="0.3">
@@ -6157,7 +6157,7 @@
       <c r="J204" s="2"/>
       <c r="K204" s="1"/>
       <c r="M204" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="205" spans="4:13" x14ac:dyDescent="0.3">
@@ -6195,7 +6195,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
       <c r="M206" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="207" spans="4:13" x14ac:dyDescent="0.3">
@@ -6291,7 +6291,7 @@
       <c r="J210" s="2"/>
       <c r="K210" s="1"/>
       <c r="M210" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="211" spans="4:13" x14ac:dyDescent="0.3">
@@ -6711,7 +6711,7 @@
         <v>40</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>13</v>
@@ -6740,7 +6740,7 @@
         <v>65</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>13</v>
@@ -6769,7 +6769,7 @@
         <v>60</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>13</v>
@@ -6798,7 +6798,7 @@
         <v>57</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>10</v>
@@ -6827,7 +6827,7 @@
         <v>41</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>61</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -6885,7 +6885,7 @@
         <v>58</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>13</v>
@@ -6914,7 +6914,7 @@
         <v>45</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>10</v>
@@ -6943,7 +6943,7 @@
         <v>46</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>10</v>
@@ -6972,7 +6972,7 @@
         <v>47</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>10</v>
@@ -7001,7 +7001,7 @@
         <v>55</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>13</v>
@@ -7030,7 +7030,7 @@
         <v>48</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>10</v>
@@ -7059,7 +7059,7 @@
         <v>49</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>10</v>
@@ -7088,7 +7088,7 @@
         <v>66</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>10</v>
@@ -7117,7 +7117,7 @@
         <v>62</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -7146,7 +7146,7 @@
         <v>51</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>12</v>
@@ -7170,7 +7170,7 @@
       <c r="J241" s="2"/>
       <c r="K241" s="1"/>
       <c r="M241" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="242" spans="4:13" x14ac:dyDescent="0.3">
@@ -7184,7 +7184,7 @@
         <v>52</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>13</v>
@@ -7213,7 +7213,7 @@
         <v>59</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>10</v>
@@ -7242,7 +7242,7 @@
         <v>53</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>13</v>
@@ -7271,7 +7271,7 @@
         <v>40</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>13</v>
@@ -7300,7 +7300,7 @@
         <v>60</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>13</v>
@@ -7329,7 +7329,7 @@
         <v>41</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>10</v>
@@ -7358,7 +7358,7 @@
         <v>61</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>10</v>
@@ -7387,7 +7387,7 @@
         <v>45</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>12</v>
@@ -7411,7 +7411,7 @@
       <c r="J250" s="2"/>
       <c r="K250" s="1"/>
       <c r="M250" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="251" spans="4:13" x14ac:dyDescent="0.3">
@@ -7425,7 +7425,7 @@
         <v>46</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>10</v>
@@ -7454,7 +7454,7 @@
         <v>47</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7483,7 +7483,7 @@
         <v>64</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>10</v>
@@ -7512,7 +7512,7 @@
         <v>48</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>10</v>
@@ -7541,7 +7541,7 @@
         <v>49</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -7570,7 +7570,7 @@
         <v>66</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>13</v>
@@ -7599,7 +7599,7 @@
         <v>51</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -7628,7 +7628,7 @@
         <v>52</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>13</v>
@@ -7657,7 +7657,7 @@
         <v>59</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -7686,7 +7686,7 @@
         <v>40</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>13</v>
@@ -7715,7 +7715,7 @@
         <v>60</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>13</v>
@@ -7744,7 +7744,7 @@
         <v>41</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>14</v>
@@ -7768,7 +7768,7 @@
       <c r="J263" s="2"/>
       <c r="K263" s="1"/>
       <c r="M263" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="264" spans="4:13" x14ac:dyDescent="0.3">
@@ -7782,7 +7782,7 @@
         <v>61</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>10</v>
@@ -7811,7 +7811,7 @@
         <v>67</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>13</v>
@@ -7840,7 +7840,7 @@
         <v>45</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>10</v>
@@ -7869,7 +7869,7 @@
         <v>46</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>10</v>
@@ -7898,7 +7898,7 @@
         <v>47</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>13</v>
@@ -7927,7 +7927,7 @@
         <v>68</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>12</v>
@@ -7951,7 +7951,7 @@
       <c r="J270" s="2"/>
       <c r="K270" s="1"/>
       <c r="M270" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="271" spans="4:13" x14ac:dyDescent="0.3">
@@ -7965,7 +7965,7 @@
         <v>64</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>12</v>
@@ -7989,7 +7989,7 @@
       <c r="J272" s="2"/>
       <c r="K272" s="1"/>
       <c r="M272" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="273" spans="4:13" x14ac:dyDescent="0.3">
@@ -8003,7 +8003,7 @@
         <v>48</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>10</v>
@@ -8032,7 +8032,7 @@
         <v>49</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>10</v>
@@ -8061,7 +8061,7 @@
         <v>66</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>13</v>
@@ -8090,7 +8090,7 @@
         <v>51</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>13</v>
@@ -8119,7 +8119,7 @@
         <v>52</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>13</v>
@@ -8148,7 +8148,7 @@
         <v>69</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>13</v>
@@ -8177,7 +8177,7 @@
         <v>59</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>13</v>
@@ -8206,7 +8206,7 @@
         <v>40</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>13</v>
@@ -8235,7 +8235,7 @@
         <v>70</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>10</v>
@@ -8264,7 +8264,7 @@
         <v>60</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>13</v>
@@ -8293,7 +8293,7 @@
         <v>41</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>12</v>
@@ -8317,7 +8317,7 @@
       <c r="J284" s="2"/>
       <c r="K284" s="1"/>
       <c r="M284" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="285" spans="4:13" x14ac:dyDescent="0.3">
@@ -8331,7 +8331,7 @@
         <v>67</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>13</v>
@@ -8360,7 +8360,7 @@
         <v>45</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>10</v>
@@ -8389,7 +8389,7 @@
         <v>46</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>13</v>
@@ -8418,7 +8418,7 @@
         <v>47</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>13</v>
@@ -8447,7 +8447,7 @@
         <v>68</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>12</v>
@@ -8471,7 +8471,7 @@
       <c r="J290" s="2"/>
       <c r="K290" s="1"/>
       <c r="M290" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="291" spans="4:13" x14ac:dyDescent="0.3">
@@ -8485,7 +8485,7 @@
         <v>64</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>12</v>
@@ -8509,7 +8509,7 @@
       <c r="J292" s="2"/>
       <c r="K292" s="1"/>
       <c r="M292" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="293" spans="4:13" x14ac:dyDescent="0.3">
@@ -8523,7 +8523,7 @@
         <v>48</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>49</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>10</v>
@@ -8581,7 +8581,7 @@
         <v>66</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>13</v>
@@ -8610,7 +8610,7 @@
         <v>51</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>10</v>
@@ -8639,7 +8639,7 @@
         <v>52</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>13</v>
@@ -8668,7 +8668,7 @@
         <v>69</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>13</v>
@@ -8697,7 +8697,7 @@
         <v>59</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>12</v>
@@ -8721,7 +8721,7 @@
       <c r="J300" s="2"/>
       <c r="K300" s="1"/>
       <c r="M300" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="301" spans="4:13" x14ac:dyDescent="0.3">
@@ -8846,7 +8846,7 @@
       <c r="J305" s="2"/>
       <c r="K305" s="1"/>
       <c r="M305" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="306" spans="4:13" x14ac:dyDescent="0.3">
@@ -8942,7 +8942,7 @@
       <c r="J309" s="2"/>
       <c r="K309" s="1"/>
       <c r="M309" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="310" spans="4:13" x14ac:dyDescent="0.3">
@@ -9188,7 +9188,7 @@
         <v>40</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>13</v>
@@ -9217,7 +9217,7 @@
         <v>60</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>13</v>
@@ -9246,7 +9246,7 @@
         <v>41</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>14</v>
@@ -9270,7 +9270,7 @@
       <c r="J321" s="2"/>
       <c r="K321" s="1"/>
       <c r="M321" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="322" spans="4:13" x14ac:dyDescent="0.3">
@@ -9284,7 +9284,7 @@
         <v>45</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>13</v>
@@ -9313,7 +9313,7 @@
         <v>71</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>13</v>
@@ -9342,7 +9342,7 @@
         <v>47</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>13</v>
@@ -9371,7 +9371,7 @@
         <v>68</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>13</v>
@@ -9400,7 +9400,7 @@
         <v>64</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>14</v>
@@ -9424,7 +9424,7 @@
       <c r="J327" s="2"/>
       <c r="K327" s="1"/>
       <c r="M327" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="328" spans="4:13" x14ac:dyDescent="0.3">
@@ -9438,7 +9438,7 @@
         <v>48</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>13</v>
@@ -9467,7 +9467,7 @@
         <v>49</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>10</v>
@@ -9496,7 +9496,7 @@
         <v>66</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>13</v>
@@ -9525,7 +9525,7 @@
         <v>51</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>10</v>
@@ -9554,7 +9554,7 @@
         <v>52</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>13</v>
@@ -9583,7 +9583,7 @@
         <v>69</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>13</v>
@@ -9612,7 +9612,7 @@
         <v>59</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>10</v>
@@ -9641,7 +9641,7 @@
         <v>40</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>14</v>
@@ -9665,7 +9665,7 @@
       <c r="J336" s="2"/>
       <c r="K336" s="1"/>
       <c r="M336" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="337" spans="4:13" x14ac:dyDescent="0.3">
@@ -9679,7 +9679,7 @@
         <v>60</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>13</v>
@@ -9708,7 +9708,7 @@
         <v>41</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>13</v>
@@ -9737,7 +9737,7 @@
         <v>45</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>10</v>
@@ -9766,7 +9766,7 @@
         <v>71</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>10</v>
@@ -9795,7 +9795,7 @@
         <v>47</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>13</v>
@@ -9824,7 +9824,7 @@
         <v>68</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>13</v>
@@ -9853,7 +9853,7 @@
         <v>72</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -9882,7 +9882,7 @@
         <v>64</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>14</v>
@@ -9906,7 +9906,7 @@
       <c r="J345" s="2"/>
       <c r="K345" s="1"/>
       <c r="M345" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="346" spans="4:13" x14ac:dyDescent="0.3">
@@ -9920,7 +9920,7 @@
         <v>48</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>13</v>
@@ -9949,7 +9949,7 @@
         <v>49</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>10</v>
@@ -9978,7 +9978,7 @@
         <v>66</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>13</v>
@@ -10007,7 +10007,7 @@
         <v>51</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>13</v>
@@ -10036,7 +10036,7 @@
         <v>52</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>13</v>
@@ -10065,7 +10065,7 @@
         <v>69</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>13</v>
@@ -10094,7 +10094,7 @@
         <v>59</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>10</v>
@@ -10123,7 +10123,7 @@
         <v>40</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>12</v>
@@ -10147,7 +10147,7 @@
       <c r="J354" s="2"/>
       <c r="K354" s="1"/>
       <c r="M354" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="355" spans="4:13" x14ac:dyDescent="0.3">
@@ -10161,7 +10161,7 @@
         <v>70</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>10</v>
@@ -10190,7 +10190,7 @@
         <v>60</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>13</v>
@@ -10219,7 +10219,7 @@
         <v>41</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>13</v>
@@ -10248,7 +10248,7 @@
         <v>45</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>10</v>
@@ -10277,7 +10277,7 @@
         <v>71</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>13</v>
@@ -10306,7 +10306,7 @@
         <v>68</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>12</v>
@@ -10330,7 +10330,7 @@
       <c r="J361" s="2"/>
       <c r="K361" s="1"/>
       <c r="M361" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="362" spans="4:13" x14ac:dyDescent="0.3">
@@ -10344,7 +10344,7 @@
         <v>72</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>10</v>
@@ -10373,7 +10373,7 @@
         <v>64</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I363" s="1" t="s">
         <v>14</v>
@@ -10397,7 +10397,7 @@
       <c r="J364" s="2"/>
       <c r="K364" s="1"/>
       <c r="M364" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="365" spans="4:13" x14ac:dyDescent="0.3">
@@ -10411,7 +10411,7 @@
         <v>49</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I365" s="1" t="s">
         <v>10</v>
@@ -10440,7 +10440,7 @@
         <v>66</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>13</v>
@@ -10469,7 +10469,7 @@
         <v>51</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>10</v>
@@ -10498,7 +10498,7 @@
         <v>52</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>13</v>
@@ -10527,7 +10527,7 @@
         <v>69</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>13</v>
@@ -10556,7 +10556,7 @@
         <v>59</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>12</v>
@@ -10580,7 +10580,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
       <c r="M371" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="372" spans="4:13" x14ac:dyDescent="0.3">
@@ -10594,7 +10594,7 @@
         <v>40</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>12</v>
@@ -10618,7 +10618,7 @@
       <c r="J373" s="2"/>
       <c r="K373" s="1"/>
       <c r="M373" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="374" spans="4:13" x14ac:dyDescent="0.3">
@@ -10632,7 +10632,7 @@
         <v>70</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>10</v>
@@ -10661,7 +10661,7 @@
         <v>60</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>13</v>
@@ -10690,7 +10690,7 @@
         <v>41</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>10</v>
@@ -10719,7 +10719,7 @@
         <v>45</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>13</v>
@@ -10748,7 +10748,7 @@
         <v>71</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>13</v>
@@ -10777,7 +10777,7 @@
         <v>68</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>13</v>
@@ -10806,7 +10806,7 @@
         <v>72</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>10</v>
@@ -10835,7 +10835,7 @@
         <v>64</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>13</v>
@@ -10864,7 +10864,7 @@
         <v>49</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I382" s="1" t="s">
         <v>10</v>
@@ -10893,7 +10893,7 @@
         <v>66</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>10</v>
@@ -10922,7 +10922,7 @@
         <v>51</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>10</v>
@@ -10951,7 +10951,7 @@
         <v>52</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>13</v>
@@ -10980,7 +10980,7 @@
         <v>69</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>13</v>
@@ -11009,7 +11009,7 @@
         <v>59</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>12</v>
@@ -11033,7 +11033,7 @@
       <c r="J388" s="2"/>
       <c r="K388" s="1"/>
       <c r="M388" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="389" spans="4:13" x14ac:dyDescent="0.3">
@@ -11047,7 +11047,7 @@
         <v>40</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I389" s="1" t="s">
         <v>12</v>
@@ -11071,7 +11071,7 @@
       <c r="J390" s="2"/>
       <c r="K390" s="1"/>
       <c r="M390" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="391" spans="4:13" x14ac:dyDescent="0.3">
@@ -11085,7 +11085,7 @@
         <v>70</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I391" s="1" t="s">
         <v>10</v>
@@ -11114,7 +11114,7 @@
         <v>60</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I392" s="1" t="s">
         <v>12</v>
@@ -11138,7 +11138,7 @@
       <c r="J393" s="2"/>
       <c r="K393" s="1"/>
       <c r="M393" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="394" spans="4:13" x14ac:dyDescent="0.3">
@@ -11152,7 +11152,7 @@
         <v>41</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>13</v>
@@ -11181,7 +11181,7 @@
         <v>45</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>12</v>
@@ -11205,7 +11205,7 @@
       <c r="J396" s="2"/>
       <c r="K396" s="1"/>
       <c r="M396" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="397" spans="4:13" x14ac:dyDescent="0.3">
@@ -11219,7 +11219,7 @@
         <v>71</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I397" s="1" t="s">
         <v>13</v>
@@ -11248,7 +11248,7 @@
         <v>72</v>
       </c>
       <c r="H398" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I398" s="1" t="s">
         <v>10</v>
@@ -11277,7 +11277,7 @@
         <v>64</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>14</v>
@@ -11301,7 +11301,7 @@
       <c r="J400" s="2"/>
       <c r="K400" s="1"/>
       <c r="M400" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="401" spans="4:13" x14ac:dyDescent="0.3">
@@ -11315,7 +11315,7 @@
         <v>49</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I401" s="1" t="s">
         <v>10</v>
@@ -11344,7 +11344,7 @@
         <v>66</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>10</v>
@@ -11373,7 +11373,7 @@
         <v>51</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I403" s="1" t="s">
         <v>10</v>
@@ -11402,7 +11402,7 @@
         <v>52</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I404" s="1" t="s">
         <v>13</v>
@@ -11431,7 +11431,7 @@
         <v>69</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>13</v>
@@ -11460,7 +11460,7 @@
         <v>59</v>
       </c>
       <c r="H406" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I406" s="1" t="s">
         <v>12</v>
@@ -11484,7 +11484,7 @@
       <c r="J407" s="2"/>
       <c r="K407" s="1"/>
       <c r="M407" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="408" spans="4:13" x14ac:dyDescent="0.3">
@@ -11498,7 +11498,7 @@
         <v>40</v>
       </c>
       <c r="H408" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I408" s="1" t="s">
         <v>13</v>
@@ -11527,7 +11527,7 @@
         <v>70</v>
       </c>
       <c r="H409" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I409" s="1" t="s">
         <v>10</v>
@@ -11556,7 +11556,7 @@
         <v>60</v>
       </c>
       <c r="H410" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I410" s="1" t="s">
         <v>13</v>
@@ -11585,7 +11585,7 @@
         <v>41</v>
       </c>
       <c r="H411" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I411" s="1" t="s">
         <v>13</v>
@@ -11614,7 +11614,7 @@
         <v>73</v>
       </c>
       <c r="H412" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I412" s="1" t="s">
         <v>10</v>
@@ -11643,7 +11643,7 @@
         <v>45</v>
       </c>
       <c r="H413" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I413" s="1" t="s">
         <v>13</v>
@@ -11672,7 +11672,7 @@
         <v>71</v>
       </c>
       <c r="H414" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I414" s="1" t="s">
         <v>13</v>
@@ -11701,7 +11701,7 @@
         <v>72</v>
       </c>
       <c r="H415" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I415" s="1" t="s">
         <v>10</v>
@@ -11730,7 +11730,7 @@
         <v>64</v>
       </c>
       <c r="H416" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I416" s="1" t="s">
         <v>13</v>
@@ -11759,7 +11759,7 @@
         <v>49</v>
       </c>
       <c r="H417" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I417" s="1" t="s">
         <v>10</v>
@@ -11788,7 +11788,7 @@
         <v>66</v>
       </c>
       <c r="H418" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I418" s="1" t="s">
         <v>13</v>
@@ -11817,7 +11817,7 @@
         <v>51</v>
       </c>
       <c r="H419" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I419" s="1" t="s">
         <v>10</v>
@@ -11846,7 +11846,7 @@
         <v>52</v>
       </c>
       <c r="H420" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I420" s="1" t="s">
         <v>13</v>
@@ -11875,7 +11875,7 @@
         <v>69</v>
       </c>
       <c r="H421" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I421" s="1" t="s">
         <v>13</v>
@@ -11904,7 +11904,7 @@
         <v>59</v>
       </c>
       <c r="H422" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I422" s="1" t="s">
         <v>13</v>
@@ -11933,7 +11933,7 @@
         <v>74</v>
       </c>
       <c r="H423" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I423" s="1" t="s">
         <v>10</v>
@@ -11962,7 +11962,7 @@
         <v>40</v>
       </c>
       <c r="H424" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I424" s="1" t="s">
         <v>13</v>
@@ -11991,7 +11991,7 @@
         <v>70</v>
       </c>
       <c r="H425" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I425" s="1" t="s">
         <v>10</v>
@@ -12020,7 +12020,7 @@
         <v>60</v>
       </c>
       <c r="H426" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I426" s="1" t="s">
         <v>13</v>
@@ -12049,7 +12049,7 @@
         <v>41</v>
       </c>
       <c r="H427" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I427" s="1" t="s">
         <v>13</v>
@@ -12078,7 +12078,7 @@
         <v>45</v>
       </c>
       <c r="H428" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I428" s="1" t="s">
         <v>13</v>
@@ -12107,7 +12107,7 @@
         <v>72</v>
       </c>
       <c r="H429" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I429" s="1" t="s">
         <v>13</v>
@@ -12136,7 +12136,7 @@
         <v>64</v>
       </c>
       <c r="H430" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I430" s="1" t="s">
         <v>13</v>
@@ -12165,7 +12165,7 @@
         <v>49</v>
       </c>
       <c r="H431" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I431" s="1" t="s">
         <v>13</v>
@@ -12194,7 +12194,7 @@
         <v>66</v>
       </c>
       <c r="H432" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I432" s="1" t="s">
         <v>13</v>
@@ -12223,7 +12223,7 @@
         <v>51</v>
       </c>
       <c r="H433" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I433" s="1" t="s">
         <v>10</v>
@@ -12252,7 +12252,7 @@
         <v>52</v>
       </c>
       <c r="H434" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I434" s="1" t="s">
         <v>13</v>
@@ -12281,7 +12281,7 @@
         <v>69</v>
       </c>
       <c r="H435" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I435" s="1" t="s">
         <v>13</v>
@@ -12310,7 +12310,7 @@
         <v>59</v>
       </c>
       <c r="H436" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I436" s="1" t="s">
         <v>10</v>
@@ -12339,7 +12339,7 @@
         <v>74</v>
       </c>
       <c r="H437" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I437" s="1" t="s">
         <v>13</v>
@@ -12368,7 +12368,7 @@
         <v>40</v>
       </c>
       <c r="H438" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I438" s="1" t="s">
         <v>13</v>
@@ -12397,7 +12397,7 @@
         <v>70</v>
       </c>
       <c r="H439" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I439" s="1" t="s">
         <v>10</v>
@@ -12426,7 +12426,7 @@
         <v>60</v>
       </c>
       <c r="H440" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I440" s="1" t="s">
         <v>13</v>
@@ -12455,7 +12455,7 @@
         <v>41</v>
       </c>
       <c r="H441" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I441" s="1" t="s">
         <v>13</v>
@@ -12484,7 +12484,7 @@
         <v>45</v>
       </c>
       <c r="H442" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I442" s="1" t="s">
         <v>10</v>
@@ -12513,7 +12513,7 @@
         <v>72</v>
       </c>
       <c r="H443" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I443" s="1" t="s">
         <v>13</v>
@@ -12542,7 +12542,7 @@
         <v>64</v>
       </c>
       <c r="H444" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I444" s="1" t="s">
         <v>13</v>
@@ -12571,7 +12571,7 @@
         <v>49</v>
       </c>
       <c r="H445" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I445" s="1" t="s">
         <v>12</v>
@@ -12595,7 +12595,7 @@
       <c r="J446" s="2"/>
       <c r="K446" s="1"/>
       <c r="M446" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="447" spans="4:13" x14ac:dyDescent="0.3">
@@ -12609,7 +12609,7 @@
         <v>66</v>
       </c>
       <c r="H447" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I447" s="1" t="s">
         <v>13</v>
@@ -12638,7 +12638,7 @@
         <v>75</v>
       </c>
       <c r="H448" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I448" s="1" t="s">
         <v>14</v>
@@ -12662,7 +12662,7 @@
       <c r="J449" s="2"/>
       <c r="K449" s="1"/>
       <c r="M449" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="450" spans="4:13" x14ac:dyDescent="0.3">
@@ -12676,7 +12676,7 @@
         <v>51</v>
       </c>
       <c r="H450" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I450" s="1" t="s">
         <v>12</v>
@@ -12700,7 +12700,7 @@
       <c r="J451" s="2"/>
       <c r="K451" s="1"/>
       <c r="M451" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="452" spans="4:13" x14ac:dyDescent="0.3">
@@ -12714,7 +12714,7 @@
         <v>52</v>
       </c>
       <c r="H452" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I452" s="1" t="s">
         <v>13</v>
@@ -12743,7 +12743,7 @@
         <v>59</v>
       </c>
       <c r="H453" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I453" s="1" t="s">
         <v>13</v>
@@ -12772,7 +12772,7 @@
         <v>74</v>
       </c>
       <c r="H454" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>13</v>
@@ -12801,7 +12801,7 @@
         <v>40</v>
       </c>
       <c r="H455" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I455" s="1" t="s">
         <v>13</v>
@@ -12830,7 +12830,7 @@
         <v>70</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I456" s="1" t="s">
         <v>10</v>
@@ -12859,7 +12859,7 @@
         <v>60</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I457" s="1" t="s">
         <v>13</v>
@@ -12888,7 +12888,7 @@
         <v>41</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>13</v>
@@ -12917,7 +12917,7 @@
         <v>67</v>
       </c>
       <c r="H459" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I459" s="1" t="s">
         <v>13</v>
@@ -12946,7 +12946,7 @@
         <v>45</v>
       </c>
       <c r="H460" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I460" s="1" t="s">
         <v>13</v>
@@ -12975,7 +12975,7 @@
         <v>72</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I461" s="1" t="s">
         <v>13</v>
@@ -13004,7 +13004,7 @@
         <v>64</v>
       </c>
       <c r="H462" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I462" s="1" t="s">
         <v>13</v>
@@ -13033,7 +13033,7 @@
         <v>49</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I463" s="1" t="s">
         <v>10</v>
@@ -13062,7 +13062,7 @@
         <v>66</v>
       </c>
       <c r="H464" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I464" s="1" t="s">
         <v>13</v>
@@ -13091,7 +13091,7 @@
         <v>75</v>
       </c>
       <c r="H465" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I465" s="1" t="s">
         <v>10</v>
@@ -13120,7 +13120,7 @@
         <v>51</v>
       </c>
       <c r="H466" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I466" s="1" t="s">
         <v>10</v>
@@ -13149,7 +13149,7 @@
         <v>52</v>
       </c>
       <c r="H467" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I467" s="1" t="s">
         <v>13</v>
@@ -13178,7 +13178,7 @@
         <v>59</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I468" s="1" t="s">
         <v>10</v>
@@ -13207,7 +13207,7 @@
         <v>74</v>
       </c>
       <c r="H469" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I469" s="1" t="s">
         <v>13</v>
@@ -13236,7 +13236,7 @@
         <v>76</v>
       </c>
       <c r="H470" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I470" s="1" t="s">
         <v>10</v>
@@ -13265,7 +13265,7 @@
         <v>40</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I471" s="1" t="s">
         <v>13</v>
@@ -13294,7 +13294,7 @@
         <v>70</v>
       </c>
       <c r="H472" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I472" s="1" t="s">
         <v>10</v>
@@ -13323,7 +13323,7 @@
         <v>60</v>
       </c>
       <c r="H473" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I473" s="1" t="s">
         <v>13</v>
@@ -13352,7 +13352,7 @@
         <v>41</v>
       </c>
       <c r="H474" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I474" s="1" t="s">
         <v>13</v>
@@ -13381,7 +13381,7 @@
         <v>67</v>
       </c>
       <c r="H475" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I475" s="1" t="s">
         <v>13</v>
@@ -13410,7 +13410,7 @@
         <v>45</v>
       </c>
       <c r="H476" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I476" s="1" t="s">
         <v>13</v>
@@ -13439,7 +13439,7 @@
         <v>72</v>
       </c>
       <c r="H477" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I477" s="1" t="s">
         <v>13</v>
@@ -13468,7 +13468,7 @@
         <v>64</v>
       </c>
       <c r="H478" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I478" s="1" t="s">
         <v>13</v>
@@ -13497,7 +13497,7 @@
         <v>49</v>
       </c>
       <c r="H479" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I479" s="1" t="s">
         <v>13</v>
@@ -13526,7 +13526,7 @@
         <v>66</v>
       </c>
       <c r="H480" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I480" s="1" t="s">
         <v>13</v>
@@ -13555,7 +13555,7 @@
         <v>75</v>
       </c>
       <c r="H481" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I481" s="1" t="s">
         <v>13</v>
@@ -13584,7 +13584,7 @@
         <v>77</v>
       </c>
       <c r="H482" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I482" s="1" t="s">
         <v>13</v>
@@ -13613,7 +13613,7 @@
         <v>51</v>
       </c>
       <c r="H483" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I483" s="1" t="s">
         <v>13</v>
@@ -13642,7 +13642,7 @@
         <v>52</v>
       </c>
       <c r="H484" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I484" s="1" t="s">
         <v>13</v>
@@ -13671,7 +13671,7 @@
         <v>59</v>
       </c>
       <c r="H485" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I485" s="1" t="s">
         <v>10</v>
@@ -13700,7 +13700,7 @@
         <v>74</v>
       </c>
       <c r="H486" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I486" s="1" t="s">
         <v>13</v>
@@ -13729,7 +13729,7 @@
         <v>76</v>
       </c>
       <c r="H487" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I487" s="1" t="s">
         <v>10</v>
@@ -13748,150 +13748,541 @@
       </c>
     </row>
     <row r="488" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H488" s="2"/>
-      <c r="I488" s="1"/>
-      <c r="J488" s="2"/>
-      <c r="K488" s="1"/>
+      <c r="D488" t="s">
+        <v>39</v>
+      </c>
+      <c r="E488">
+        <v>1174</v>
+      </c>
+      <c r="F488" t="s">
+        <v>40</v>
+      </c>
+      <c r="H488" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I488" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J488" s="2">
+        <v>0</v>
+      </c>
+      <c r="K488" s="1">
+        <v>46219.645949074074</v>
+      </c>
+      <c r="L488">
+        <v>0</v>
+      </c>
+      <c r="M488" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="489" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H489" s="2"/>
-      <c r="I489" s="1"/>
-      <c r="J489" s="2"/>
-      <c r="K489" s="1"/>
+      <c r="D489" t="s">
+        <v>39</v>
+      </c>
+      <c r="E489">
+        <v>3777</v>
+      </c>
+      <c r="F489" t="s">
+        <v>70</v>
+      </c>
+      <c r="H489" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I489" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J489" s="2">
+        <v>0</v>
+      </c>
+      <c r="K489" s="1">
+        <v>46219.645949074074</v>
+      </c>
+      <c r="L489">
+        <v>0</v>
+      </c>
+      <c r="M489" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="490" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H490" s="2"/>
-      <c r="I490" s="1"/>
-      <c r="J490" s="2"/>
-      <c r="K490" s="1"/>
+      <c r="D490" t="s">
+        <v>39</v>
+      </c>
+      <c r="E490">
+        <v>2657</v>
+      </c>
+      <c r="F490" t="s">
+        <v>60</v>
+      </c>
+      <c r="H490" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I490" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J490" s="2">
+        <v>0</v>
+      </c>
+      <c r="K490" s="1">
+        <v>46219.646643518521</v>
+      </c>
+      <c r="L490">
+        <v>0</v>
+      </c>
+      <c r="M490" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="491" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H491" s="2"/>
-      <c r="I491" s="1"/>
-      <c r="J491" s="2"/>
-      <c r="K491" s="1"/>
+      <c r="D491" t="s">
+        <v>39</v>
+      </c>
+      <c r="E491">
+        <v>1176</v>
+      </c>
+      <c r="F491" t="s">
+        <v>41</v>
+      </c>
+      <c r="H491" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I491" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J491" s="2">
+        <v>0</v>
+      </c>
+      <c r="K491" s="1">
+        <v>46219.647337962961</v>
+      </c>
+      <c r="L491">
+        <v>0</v>
+      </c>
+      <c r="M491" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="492" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H492" s="2"/>
-      <c r="I492" s="1"/>
-      <c r="J492" s="2"/>
-      <c r="K492" s="1"/>
+      <c r="D492" t="s">
+        <v>39</v>
+      </c>
+      <c r="E492">
+        <v>1179</v>
+      </c>
+      <c r="F492" t="s">
+        <v>67</v>
+      </c>
+      <c r="H492" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I492" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J492" s="2">
+        <v>0</v>
+      </c>
+      <c r="K492" s="1">
+        <v>46219.648032407407</v>
+      </c>
+      <c r="L492">
+        <v>0</v>
+      </c>
+      <c r="M492" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="493" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H493" s="2"/>
-      <c r="I493" s="1"/>
-      <c r="J493" s="2"/>
-      <c r="K493" s="1"/>
+      <c r="D493" t="s">
+        <v>39</v>
+      </c>
+      <c r="E493">
+        <v>1180</v>
+      </c>
+      <c r="F493" t="s">
+        <v>45</v>
+      </c>
+      <c r="H493" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I493" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J493" s="2">
+        <v>6.7361111111111111E-3</v>
+      </c>
+      <c r="K493" s="1">
+        <v>46219.648726851854</v>
+      </c>
+      <c r="L493">
+        <v>0</v>
+      </c>
+      <c r="M493" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="494" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H494" s="2"/>
-      <c r="I494" s="1"/>
-      <c r="J494" s="2"/>
-      <c r="K494" s="1"/>
+      <c r="D494" t="s">
+        <v>39</v>
+      </c>
+      <c r="E494">
+        <v>4754</v>
+      </c>
+      <c r="F494" t="s">
+        <v>72</v>
+      </c>
+      <c r="H494" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I494" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J494" s="2">
+        <v>0</v>
+      </c>
+      <c r="K494" s="1">
+        <v>46219.648726851854</v>
+      </c>
+      <c r="L494">
+        <v>0</v>
+      </c>
+      <c r="M494" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="495" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H495" s="2"/>
-      <c r="I495" s="1"/>
-      <c r="J495" s="2"/>
-      <c r="K495" s="1"/>
+      <c r="D495" t="s">
+        <v>39</v>
+      </c>
+      <c r="E495">
+        <v>3114</v>
+      </c>
+      <c r="F495" t="s">
+        <v>64</v>
+      </c>
+      <c r="H495" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I495" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J495" s="2">
+        <v>0</v>
+      </c>
+      <c r="K495" s="1">
+        <v>46219.649421296293</v>
+      </c>
+      <c r="L495">
+        <v>0</v>
+      </c>
+      <c r="M495" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="496" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H496" s="2"/>
-      <c r="I496" s="1"/>
-      <c r="J496" s="2"/>
-      <c r="K496" s="1"/>
-    </row>
-    <row r="497" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H497" s="2"/>
-      <c r="I497" s="1"/>
-      <c r="J497" s="2"/>
-      <c r="K497" s="1"/>
-    </row>
-    <row r="498" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H498" s="2"/>
-      <c r="I498" s="1"/>
-      <c r="J498" s="2"/>
-      <c r="K498" s="1"/>
-    </row>
-    <row r="499" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H499" s="2"/>
-      <c r="I499" s="1"/>
-      <c r="J499" s="2"/>
-      <c r="K499" s="1"/>
-    </row>
-    <row r="500" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H500" s="2"/>
-      <c r="I500" s="1"/>
-      <c r="J500" s="2"/>
-      <c r="K500" s="1"/>
-    </row>
-    <row r="501" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H501" s="2"/>
-      <c r="I501" s="1"/>
-      <c r="J501" s="2"/>
-      <c r="K501" s="1"/>
-    </row>
-    <row r="502" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H502" s="2"/>
-      <c r="I502" s="1"/>
-      <c r="J502" s="2"/>
-      <c r="K502" s="1"/>
-    </row>
-    <row r="503" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H503" s="2"/>
-      <c r="I503" s="1"/>
-      <c r="J503" s="2"/>
-      <c r="K503" s="1"/>
-    </row>
-    <row r="504" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H504" s="2"/>
-      <c r="I504" s="1"/>
-      <c r="J504" s="2"/>
-      <c r="K504" s="1"/>
-    </row>
-    <row r="505" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D496" t="s">
+        <v>39</v>
+      </c>
+      <c r="E496">
+        <v>1183</v>
+      </c>
+      <c r="F496" t="s">
+        <v>49</v>
+      </c>
+      <c r="H496" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I496" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J496" s="2">
+        <v>8.2638888888888883E-3</v>
+      </c>
+      <c r="K496" s="1">
+        <v>46219.65011574074</v>
+      </c>
+      <c r="L496">
+        <v>0</v>
+      </c>
+      <c r="M496" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="497" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D497" t="s">
+        <v>39</v>
+      </c>
+      <c r="E497">
+        <v>3259</v>
+      </c>
+      <c r="F497" t="s">
+        <v>66</v>
+      </c>
+      <c r="H497" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I497" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J497" s="2">
+        <v>0</v>
+      </c>
+      <c r="K497" s="1">
+        <v>46219.65011574074</v>
+      </c>
+      <c r="L497">
+        <v>0</v>
+      </c>
+      <c r="M497" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="498" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D498" t="s">
+        <v>39</v>
+      </c>
+      <c r="E498">
+        <v>5389</v>
+      </c>
+      <c r="F498" t="s">
+        <v>75</v>
+      </c>
+      <c r="H498" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I498" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J498" s="2">
+        <v>0</v>
+      </c>
+      <c r="K498" s="1">
+        <v>46219.650810185187</v>
+      </c>
+      <c r="L498">
+        <v>0</v>
+      </c>
+      <c r="M498" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="499" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D499" t="s">
+        <v>39</v>
+      </c>
+      <c r="E499">
+        <v>5313</v>
+      </c>
+      <c r="F499" t="s">
+        <v>77</v>
+      </c>
+      <c r="H499" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I499" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J499" s="2">
+        <v>0</v>
+      </c>
+      <c r="K499" s="1">
+        <v>46219.651504629626</v>
+      </c>
+      <c r="L499">
+        <v>0</v>
+      </c>
+      <c r="M499" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="500" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D500" t="s">
+        <v>39</v>
+      </c>
+      <c r="E500">
+        <v>1187</v>
+      </c>
+      <c r="F500" t="s">
+        <v>51</v>
+      </c>
+      <c r="H500" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I500" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J500" s="2">
+        <v>0</v>
+      </c>
+      <c r="K500" s="1">
+        <v>46219.651504629626</v>
+      </c>
+      <c r="L500">
+        <v>0</v>
+      </c>
+      <c r="M500" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="501" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D501" t="s">
+        <v>39</v>
+      </c>
+      <c r="E501">
+        <v>1188</v>
+      </c>
+      <c r="F501" t="s">
+        <v>52</v>
+      </c>
+      <c r="H501" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I501" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J501" s="2">
+        <v>0</v>
+      </c>
+      <c r="K501" s="1">
+        <v>46219.627314814818</v>
+      </c>
+      <c r="L501">
+        <v>0</v>
+      </c>
+      <c r="M501" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="502" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D502" t="s">
+        <v>39</v>
+      </c>
+      <c r="E502">
+        <v>2044</v>
+      </c>
+      <c r="F502" t="s">
+        <v>59</v>
+      </c>
+      <c r="H502" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I502" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J502" s="2">
+        <v>0</v>
+      </c>
+      <c r="K502" s="1">
+        <v>46219.628009259257</v>
+      </c>
+      <c r="L502">
+        <v>0</v>
+      </c>
+      <c r="M502" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="503" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D503" t="s">
+        <v>39</v>
+      </c>
+      <c r="E503">
+        <v>5156</v>
+      </c>
+      <c r="F503" t="s">
+        <v>74</v>
+      </c>
+      <c r="H503" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I503" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J503" s="2">
+        <v>0</v>
+      </c>
+      <c r="K503" s="1">
+        <v>46219.628009259257</v>
+      </c>
+      <c r="L503">
+        <v>0</v>
+      </c>
+      <c r="M503" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="504" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D504" t="s">
+        <v>39</v>
+      </c>
+      <c r="E504">
+        <v>5459</v>
+      </c>
+      <c r="F504" t="s">
+        <v>76</v>
+      </c>
+      <c r="H504" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I504" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J504" s="2">
+        <v>0</v>
+      </c>
+      <c r="K504" s="1">
+        <v>46219.628703703704</v>
+      </c>
+      <c r="L504">
+        <v>0</v>
+      </c>
+      <c r="M504" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="505" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H505" s="2"/>
       <c r="I505" s="1"/>
       <c r="J505" s="2"/>
       <c r="K505" s="1"/>
     </row>
-    <row r="506" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="506" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H506" s="2"/>
       <c r="I506" s="1"/>
       <c r="J506" s="2"/>
       <c r="K506" s="1"/>
     </row>
-    <row r="507" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="507" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H507" s="2"/>
       <c r="I507" s="1"/>
       <c r="J507" s="2"/>
       <c r="K507" s="1"/>
     </row>
-    <row r="508" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="508" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H508" s="2"/>
       <c r="I508" s="1"/>
       <c r="J508" s="2"/>
       <c r="K508" s="1"/>
     </row>
-    <row r="509" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="509" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H509" s="2"/>
       <c r="I509" s="1"/>
       <c r="J509" s="2"/>
       <c r="K509" s="1"/>
     </row>
-    <row r="510" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="510" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H510" s="2"/>
       <c r="I510" s="1"/>
       <c r="J510" s="2"/>
       <c r="K510" s="1"/>
     </row>
-    <row r="511" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="511" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H511" s="2"/>
       <c r="I511" s="1"/>
       <c r="J511" s="2"/>
       <c r="K511" s="1"/>
     </row>
-    <row r="512" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="512" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H512" s="2"/>
       <c r="I512" s="1"/>
       <c r="J512" s="2"/>
@@ -15510,6 +15901,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -15539,6 +15931,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -15604,6 +15997,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -15627,6 +16021,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -15644,6 +16039,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -15661,6 +16057,7 @@
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -15780,6 +16177,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -15863,6 +16261,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -15886,6 +16285,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -15897,6 +16297,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -15908,6 +16309,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -15955,6 +16357,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -16008,6 +16411,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -16180,6 +16584,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -16191,6 +16596,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -16268,6 +16674,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -16285,6 +16692,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -16332,6 +16740,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -16444,6 +16853,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -16503,6 +16913,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -16514,6 +16925,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -16585,6 +16997,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -16637,6 +17050,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -16713,11 +17127,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -16777,6 +17193,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -16788,6 +17205,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -16799,11 +17217,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -16857,6 +17277,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -16873,6 +17294,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -16896,6 +17318,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -16913,6 +17336,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -16959,11 +17383,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -17005,11 +17431,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -17027,6 +17455,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -17038,6 +17467,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -17049,6 +17479,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -17066,6 +17497,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -17143,6 +17575,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -17172,6 +17605,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -17183,16 +17617,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -17204,16 +17641,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -17225,11 +17665,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -17253,6 +17695,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -17294,6 +17737,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -17323,21 +17767,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -17349,6 +17797,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -17366,6 +17815,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -17405,11 +17855,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -17457,6 +17909,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -17486,6 +17939,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -17562,6 +18016,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -17608,6 +18063,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -17643,11 +18099,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -17664,6 +18122,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -17674,6 +18133,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -17709,6 +18169,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -17720,6 +18181,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -17731,6 +18193,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -17742,6 +18205,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -17753,6 +18217,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -17794,6 +18259,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -17811,6 +18277,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -17828,6 +18295,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -17869,6 +18337,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -17892,6 +18361,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -17938,6 +18408,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -17973,6 +18444,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -17996,6 +18468,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -18036,6 +18509,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -18053,11 +18527,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -18116,6 +18592,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -18132,6 +18609,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -18143,6 +18621,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -18154,11 +18633,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -18194,6 +18675,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -18246,6 +18728,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -18256,6 +18739,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -18271,6 +18755,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -18294,16 +18779,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -18374,6 +18862,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -18385,6 +18874,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -18485,6 +18975,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -18541,6 +19033,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -18564,6 +19057,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -18688,6 +19182,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -18846,6 +19341,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -18863,6 +19359,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -18903,6 +19400,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -19235,6 +19733,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -19323,6 +19822,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -19416,6 +19916,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -19475,11 +19976,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -19531,6 +20034,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -19572,6 +20076,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -19616,6 +20121,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -19662,11 +20168,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -19864,6 +20372,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -19893,6 +20402,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -19908,6 +20419,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -19967,6 +20479,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -20038,6 +20551,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -20079,6 +20593,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -20197,6 +20712,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -20261,6 +20777,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -20385,6 +20902,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -20611,6 +21129,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -20728,6 +21247,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -20811,6 +21331,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -20870,6 +21391,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -20893,6 +21415,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -20940,6 +21463,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -20999,6 +21523,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -21022,6 +21547,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -21039,6 +21565,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -21122,6 +21649,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -21313,6 +21841,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -49169,6 +49698,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -49176,6 +49706,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -49183,6 +49714,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -49198,6 +49730,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -49207,6 +49740,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -49214,9 +49748,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -49224,12 +49764,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -49237,12 +49780,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -49254,9 +49800,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -49271,6 +49819,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -49297,6 +49846,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -49307,7 +49857,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -49315,6 +49870,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -49326,6 +49882,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -49333,6 +49890,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -49347,13 +49905,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -49364,15 +49928,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -49388,6 +49955,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -49406,6 +49974,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -49417,6 +49986,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -49434,18 +50004,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -49474,6 +50049,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -49481,9 +50057,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -49506,12 +50084,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -49526,9 +50107,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -49544,12 +50127,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -49570,6 +50155,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -49581,9 +50167,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -49595,6 +50183,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -49634,9 +50223,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -49644,9 +50235,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -49657,6 +50250,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -49664,18 +50258,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -49683,6 +50285,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -49693,6 +50296,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -49719,15 +50323,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -49749,6 +50357,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -49756,9 +50365,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -49766,6 +50377,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -49777,6 +50389,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -49791,6 +50404,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -49800,6 +50417,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -49811,6 +50429,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -49821,10 +50440,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -49832,6 +50456,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -49846,6 +50471,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -49868,6 +50494,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -49887,25 +50514,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -49913,6 +50552,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -49920,15 +50560,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -49942,6 +50589,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -49960,9 +50608,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -49970,9 +50620,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -49980,6 +50632,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -49996,10 +50649,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
